--- a/data/RECAUDO_VU.xlsx
+++ b/data/RECAUDO_VU.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU238"/>
+  <dimension ref="A1:AU240"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -680,10 +680,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE2">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="AF2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -808,10 +808,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE3">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="AF3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG3">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE4">
-        <v>-36</v>
+        <v>-35</v>
       </c>
       <c r="AF4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG4">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE5">
-        <v>-35</v>
+        <v>-34</v>
       </c>
       <c r="AF5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG5">
         <v>0</v>
@@ -1183,10 +1183,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE6">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG6">
         <v>0</v>
@@ -1305,10 +1305,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE7">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG7">
         <v>0</v>
@@ -1430,10 +1430,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE8">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AF8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AG8">
         <v>0</v>
@@ -1558,10 +1558,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE9">
-        <v>-138</v>
+        <v>-137</v>
       </c>
       <c r="AF9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG9">
         <v>0</v>
@@ -1686,10 +1686,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE10">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG10">
         <v>0</v>
@@ -1811,10 +1811,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG11">
         <v>0</v>
@@ -1939,10 +1939,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG12">
         <v>0</v>
@@ -2067,10 +2067,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG13">
         <v>0</v>
@@ -2198,10 +2198,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE14">
-        <v>-92</v>
+        <v>-91</v>
       </c>
       <c r="AF14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG14">
         <v>0</v>
@@ -2326,10 +2326,10 @@
         <v>HASTA 30 D</v>
       </c>
       <c r="AE15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG15">
         <v>0</v>
@@ -2454,10 +2454,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE16">
-        <v>-72</v>
+        <v>-71</v>
       </c>
       <c r="AF16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG16">
         <v>0</v>
@@ -2579,10 +2579,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE17">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AF17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG17">
         <v>0</v>
@@ -2704,10 +2704,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE18">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AF18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG18">
         <v>0</v>
@@ -2829,10 +2829,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE19">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG19">
         <v>0</v>
@@ -2951,10 +2951,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE20">
-        <v>-61</v>
+        <v>-60</v>
       </c>
       <c r="AF20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG20">
         <v>0</v>
@@ -3073,10 +3073,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE21">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG21">
         <v>0</v>
@@ -3195,10 +3195,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE22">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="AF22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG22">
         <v>0</v>
@@ -3317,10 +3317,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE23">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="AF23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG23">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>HASTA 30 D</v>
       </c>
       <c r="AE24">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AF24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG24">
         <v>0</v>
@@ -3576,10 +3576,10 @@
         <v>HASTA 30 D</v>
       </c>
       <c r="AE25">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AF25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG25">
         <v>0</v>
@@ -3704,10 +3704,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE26">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="AF26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG26">
         <v>0</v>
@@ -3832,10 +3832,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE27">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG27">
         <v>0</v>
@@ -3960,10 +3960,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE28">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG28">
         <v>0</v>
@@ -4082,10 +4082,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE29">
-        <v>-36</v>
+        <v>-35</v>
       </c>
       <c r="AF29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG29">
         <v>0</v>
@@ -4210,10 +4210,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE30">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="AF30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG30">
         <v>0</v>
@@ -4338,10 +4338,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE31">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="AF31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG31">
         <v>0</v>
@@ -4469,10 +4469,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE32">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG32">
         <v>0</v>
@@ -4597,10 +4597,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE33">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="AF33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG33">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE34">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG34">
         <v>0</v>
@@ -4847,7 +4847,7 @@
         <v>PAGADO</v>
       </c>
       <c r="AF35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG35">
         <v>0</v>
@@ -4972,7 +4972,7 @@
         <v>PAGADO</v>
       </c>
       <c r="AF36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG36">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE37">
-        <v>-123</v>
+        <v>-122</v>
       </c>
       <c r="AF37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG37">
         <v>0</v>
@@ -5222,10 +5222,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE38">
-        <v>-123</v>
+        <v>-122</v>
       </c>
       <c r="AF38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG38">
         <v>0</v>
@@ -5350,10 +5350,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE39">
-        <v>-123</v>
+        <v>-122</v>
       </c>
       <c r="AF39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG39">
         <v>0</v>
@@ -5478,10 +5478,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE40">
-        <v>-123</v>
+        <v>-122</v>
       </c>
       <c r="AF40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG40">
         <v>0</v>
@@ -5603,10 +5603,10 @@
         <v>HASTA 30 D</v>
       </c>
       <c r="AE41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF41">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG41">
         <v>0</v>
@@ -5728,10 +5728,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE42">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG42">
         <v>0</v>
@@ -5853,10 +5853,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE43">
-        <v>-61</v>
+        <v>-60</v>
       </c>
       <c r="AF43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG43">
         <v>0</v>
@@ -5975,10 +5975,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE44">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG44">
         <v>0</v>
@@ -6094,10 +6094,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE45">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG45">
         <v>0</v>
@@ -6219,10 +6219,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE46">
-        <v>-61</v>
+        <v>-60</v>
       </c>
       <c r="AF46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG46">
         <v>0</v>
@@ -6344,10 +6344,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE47">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG47">
         <v>0</v>
@@ -6472,10 +6472,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE48">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG48">
         <v>0</v>
@@ -6597,13 +6597,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD49" t="str">
-        <v>HASTA 60 D</v>
+        <v>HASTA 90 D</v>
       </c>
       <c r="AE49">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AF49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG49">
         <v>0</v>
@@ -6725,10 +6725,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE50">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG50">
         <v>0</v>
@@ -6844,10 +6844,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE51">
-        <v>-61</v>
+        <v>-60</v>
       </c>
       <c r="AF51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG51">
         <v>0</v>
@@ -6966,10 +6966,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE52">
-        <v>-61</v>
+        <v>-60</v>
       </c>
       <c r="AF52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG52">
         <v>0</v>
@@ -7091,10 +7091,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE53">
-        <v>-61</v>
+        <v>-60</v>
       </c>
       <c r="AF53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG53">
         <v>0</v>
@@ -7219,10 +7219,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE54">
-        <v>-61</v>
+        <v>-60</v>
       </c>
       <c r="AF54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG54">
         <v>0</v>
@@ -7347,7 +7347,7 @@
         <v>PAGADO</v>
       </c>
       <c r="AF55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG55">
         <v>0</v>
@@ -7466,10 +7466,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE56">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="AF56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG56">
         <v>0</v>
@@ -7591,10 +7591,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE57">
-        <v>-26</v>
+        <v>-25</v>
       </c>
       <c r="AF57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG57">
         <v>0</v>
@@ -7719,10 +7719,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE58">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF58">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AG58">
         <v>0</v>
@@ -7847,10 +7847,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE59">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="AF59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG59">
         <v>0</v>
@@ -7975,10 +7975,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE60">
-        <v>-33</v>
+        <v>-32</v>
       </c>
       <c r="AF60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG60">
         <v>0</v>
@@ -8103,10 +8103,10 @@
         <v>HASTA 30 D</v>
       </c>
       <c r="AE61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG61">
         <v>0</v>
@@ -8228,7 +8228,7 @@
         <v>PAGADO</v>
       </c>
       <c r="AF62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG62">
         <v>0</v>
@@ -8347,10 +8347,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE63">
-        <v>-41</v>
+        <v>-40</v>
       </c>
       <c r="AF63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG63">
         <v>0</v>
@@ -8472,10 +8472,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE64">
-        <v>-34</v>
+        <v>-33</v>
       </c>
       <c r="AF64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG64">
         <v>0</v>
@@ -8597,10 +8597,10 @@
         <v>HASTA 60 D</v>
       </c>
       <c r="AE65">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AF65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG65">
         <v>0</v>
@@ -8725,10 +8725,10 @@
         <v>HASTA 60 D</v>
       </c>
       <c r="AE66">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AF66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG66">
         <v>0</v>
@@ -8850,10 +8850,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG67">
         <v>0</v>
@@ -8978,10 +8978,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE68">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="AF68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG68">
         <v>0</v>
@@ -9106,7 +9106,7 @@
         <v>PAGADO</v>
       </c>
       <c r="AF69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG69">
         <v>0</v>
@@ -9225,10 +9225,10 @@
         <v>MAS DE 120 D</v>
       </c>
       <c r="AE70">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG70">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>MAS DE 120 D</v>
       </c>
       <c r="AE71">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG71">
         <v>0</v>
@@ -9478,10 +9478,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE72">
-        <v>-28</v>
+        <v>-27</v>
       </c>
       <c r="AF72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG72">
         <v>0</v>
@@ -9606,10 +9606,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE73">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG73">
         <v>0</v>
@@ -9731,10 +9731,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE74">
-        <v>-38</v>
+        <v>-37</v>
       </c>
       <c r="AF74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG74">
         <v>0</v>
@@ -9856,10 +9856,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE75">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AF75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG75">
         <v>0</v>
@@ -9984,10 +9984,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE76">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AF76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG76">
         <v>0</v>
@@ -10112,10 +10112,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE77">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG77">
         <v>0</v>
@@ -10240,10 +10240,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE78">
-        <v>-32</v>
+        <v>-31</v>
       </c>
       <c r="AF78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG78">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>PAGADO</v>
       </c>
       <c r="AF79">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AG79">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE80">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG80">
         <v>0</v>
@@ -10615,10 +10615,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF81">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -10740,10 +10740,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE82">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="AF82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -10868,10 +10868,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE83">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="AF83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -10996,10 +10996,10 @@
         <v>MAS DE 120 D</v>
       </c>
       <c r="AE84">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AF84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG84">
         <v>0</v>
@@ -11118,10 +11118,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE85">
-        <v>-33</v>
+        <v>-32</v>
       </c>
       <c r="AF85">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG85">
         <v>0</v>
@@ -11246,10 +11246,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE86">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -11371,10 +11371,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE87">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF87">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG87">
         <v>0</v>
@@ -11496,10 +11496,10 @@
         <v>HASTA 30 D</v>
       </c>
       <c r="AE88">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -11624,10 +11624,10 @@
         <v>HASTA 30 D</v>
       </c>
       <c r="AE89">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF89">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -11752,10 +11752,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE90">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG90">
         <v>0</v>
@@ -11874,10 +11874,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE91">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG91">
         <v>0</v>
@@ -11996,10 +11996,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE92">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG92">
         <v>0</v>
@@ -12121,10 +12121,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE93">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG93">
         <v>0</v>
@@ -12246,10 +12246,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE94">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF94">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG94">
         <v>0</v>
@@ -12371,10 +12371,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE95">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="AF95">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG95">
         <v>0</v>
@@ -12499,10 +12499,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE96">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="AF96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG96">
         <v>0</v>
@@ -12627,10 +12627,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE97">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="AF97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG97">
         <v>0</v>
@@ -12752,10 +12752,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE98">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="AF98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG98">
         <v>0</v>
@@ -12874,10 +12874,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE99">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="AF99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG99">
         <v>0</v>
@@ -12996,10 +12996,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE100">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="AF100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG100">
         <v>0</v>
@@ -13118,10 +13118,10 @@
         <v>HASTA 30 D</v>
       </c>
       <c r="AE101">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG101">
         <v>0</v>
@@ -13243,10 +13243,10 @@
         <v>HASTA 30 D</v>
       </c>
       <c r="AE102">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF102">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG102">
         <v>0</v>
@@ -13371,10 +13371,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE103">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF103">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG103">
         <v>0</v>
@@ -13496,10 +13496,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF104">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG104">
         <v>0</v>
@@ -13621,10 +13621,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG105">
         <v>0</v>
@@ -13749,10 +13749,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE106">
-        <v>-36</v>
+        <v>-35</v>
       </c>
       <c r="AF106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG106">
         <v>0</v>
@@ -13880,10 +13880,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE107">
-        <v>-36</v>
+        <v>-35</v>
       </c>
       <c r="AF107">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG107">
         <v>0</v>
@@ -14011,10 +14011,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE108">
-        <v>-36</v>
+        <v>-35</v>
       </c>
       <c r="AF108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG108">
         <v>0</v>
@@ -14142,10 +14142,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE109">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF109">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG109">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE110">
-        <v>-22</v>
+        <v>-21</v>
       </c>
       <c r="AF110">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG110">
         <v>0</v>
@@ -14395,10 +14395,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE111">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="AF111">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG111">
         <v>0</v>
@@ -14520,10 +14520,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE112">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="AF112">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG112">
         <v>0</v>
@@ -14645,10 +14645,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF113">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG113">
         <v>0</v>
@@ -14770,10 +14770,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE114">
-        <v>-182</v>
+        <v>-181</v>
       </c>
       <c r="AF114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG114">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE115">
-        <v>-182</v>
+        <v>-181</v>
       </c>
       <c r="AF115">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG115">
         <v>0</v>
@@ -15026,10 +15026,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE116">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF116">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG116">
         <v>0</v>
@@ -15154,10 +15154,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE117">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF117">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG117">
         <v>0</v>
@@ -15282,10 +15282,10 @@
         <v>MAS DE 120 D</v>
       </c>
       <c r="AE118">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AF118">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG118">
         <v>0</v>
@@ -15407,10 +15407,10 @@
         <v>MAS DE 120 D</v>
       </c>
       <c r="AE119">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AF119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG119">
         <v>0</v>
@@ -15532,10 +15532,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE120">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="AF120">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG120">
         <v>0</v>
@@ -15660,10 +15660,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE121">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF121">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG121">
         <v>0</v>
@@ -15785,10 +15785,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE122">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF122">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG122">
         <v>0</v>
@@ -15907,10 +15907,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE123">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF123">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG123">
         <v>0</v>
@@ -16032,10 +16032,10 @@
         <v>HASTA 30 D</v>
       </c>
       <c r="AE124">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG124">
         <v>0</v>
@@ -16160,10 +16160,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE125">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG125">
         <v>0</v>
@@ -16285,10 +16285,10 @@
         <v>HASTA 120 D</v>
       </c>
       <c r="AE126">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AF126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG126">
         <v>0</v>
@@ -16407,10 +16407,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE127">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF127">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG127">
         <v>0</v>
@@ -16532,10 +16532,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE128">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="AF128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG128">
         <v>0</v>
@@ -16657,10 +16657,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE129">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG129">
         <v>0</v>
@@ -16785,10 +16785,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG130">
         <v>0</v>
@@ -16910,7 +16910,7 @@
         <v>PAGADO</v>
       </c>
       <c r="AF131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG131">
         <v>0</v>
@@ -17029,10 +17029,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE132">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="AF132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG132">
         <v>0</v>
@@ -17154,10 +17154,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE133">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF133">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG133">
         <v>0</v>
@@ -17279,10 +17279,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE134">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG134">
         <v>0</v>
@@ -17404,10 +17404,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE135">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG135">
         <v>0</v>
@@ -17532,10 +17532,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE136">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF136">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG136">
         <v>0</v>
@@ -17657,13 +17657,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD137" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE137">
-        <v>-61</v>
+        <v>-60</v>
       </c>
       <c r="AF137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG137">
         <v>0</v>
@@ -17782,13 +17782,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD138" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE138">
-        <v>-61</v>
+        <v>-60</v>
       </c>
       <c r="AF138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG138">
         <v>0</v>
@@ -17907,13 +17907,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD139" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE139">
-        <v>-61</v>
+        <v>-60</v>
       </c>
       <c r="AF139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG139">
         <v>0</v>
@@ -18032,13 +18032,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD140" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE140">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="AF140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG140">
         <v>0</v>
@@ -18160,13 +18160,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD141" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE141">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="AF141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG141">
         <v>0</v>
@@ -18288,13 +18288,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD142" t="str">
-        <v>HASTA 120 D</v>
+        <v>HASTA 90 D</v>
       </c>
       <c r="AE142">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF142">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG142">
         <v>0</v>
@@ -18413,10 +18413,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE143">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF143">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG143">
         <v>0</v>
@@ -18532,13 +18532,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD144" t="str">
-        <v>HASTA 60 D</v>
+        <v>HASTA 30 D</v>
       </c>
       <c r="AE144">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF144">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG144">
         <v>0</v>
@@ -18654,13 +18654,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD145" t="str">
-        <v>HASTA 60 D</v>
+        <v>HASTA 30 D</v>
       </c>
       <c r="AE145">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF145">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG145">
         <v>0</v>
@@ -18779,13 +18779,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD146" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE146">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="AF146">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG146">
         <v>0</v>
@@ -18907,10 +18907,10 @@
         <v>HASTA 30 D</v>
       </c>
       <c r="AE147">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF147">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG147">
         <v>0</v>
@@ -19029,13 +19029,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD148" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF148">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG148">
         <v>0</v>
@@ -19154,13 +19154,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD149" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF149">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG149">
         <v>0</v>
@@ -19279,13 +19279,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD150" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF150">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG150">
         <v>0</v>
@@ -19407,13 +19407,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD151" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE151">
-        <v>-28</v>
+        <v>-27</v>
       </c>
       <c r="AF151">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG151">
         <v>0</v>
@@ -19538,10 +19538,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE152">
-        <v>-128</v>
+        <v>-127</v>
       </c>
       <c r="AF152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG152">
         <v>0</v>
@@ -19660,13 +19660,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD153" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE153">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="AF153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG153">
         <v>0</v>
@@ -19785,10 +19785,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE154">
-        <v>-35</v>
+        <v>-34</v>
       </c>
       <c r="AF154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG154">
         <v>0</v>
@@ -19907,13 +19907,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD155" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE155">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="AF155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG155">
         <v>0</v>
@@ -20035,13 +20035,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD156" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE156">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="AF156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG156">
         <v>0</v>
@@ -20166,10 +20166,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE157">
-        <v>-40</v>
+        <v>-39</v>
       </c>
       <c r="AF157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG157">
         <v>0</v>
@@ -20294,10 +20294,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE158">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AF158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG158">
         <v>0</v>
@@ -20419,10 +20419,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE159">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AF159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG159">
         <v>0</v>
@@ -20541,10 +20541,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE160">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF160">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG160">
         <v>0</v>
@@ -20663,10 +20663,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE161">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF161">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG161">
         <v>0</v>
@@ -20785,10 +20785,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE162">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF162">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG162">
         <v>0</v>
@@ -20910,10 +20910,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE163">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF163">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG163">
         <v>0</v>
@@ -21035,10 +21035,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE164">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG164">
         <v>0</v>
@@ -21160,10 +21160,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE165">
-        <v>-61</v>
+        <v>-60</v>
       </c>
       <c r="AF165">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG165">
         <v>0</v>
@@ -21285,10 +21285,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE166">
-        <v>-61</v>
+        <v>-60</v>
       </c>
       <c r="AF166">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG166">
         <v>0</v>
@@ -21410,13 +21410,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD167" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE167">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="AF167">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG167">
         <v>0</v>
@@ -21541,10 +21541,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE168">
-        <v>-36</v>
+        <v>-35</v>
       </c>
       <c r="AF168">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG168">
         <v>0</v>
@@ -21666,10 +21666,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE169">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG169">
         <v>0</v>
@@ -21794,13 +21794,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD170" t="str">
-        <v>HASTA 120 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE170">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="AF170">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG170">
         <v>0</v>
@@ -21925,13 +21925,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD171" t="str">
-        <v>HASTA 120 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE171">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="AF171">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG171">
         <v>0</v>
@@ -22056,13 +22056,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD172" t="str">
-        <v>HASTA 120 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE172">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="AF172">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG172">
         <v>0</v>
@@ -22187,13 +22187,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD173" t="str">
-        <v>HASTA 120 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE173">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="AF173">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG173">
         <v>0</v>
@@ -22318,13 +22318,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD174" t="str">
-        <v>HASTA 120 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE174">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="AF174">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG174">
         <v>0</v>
@@ -22446,13 +22446,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD175" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE175">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="AF175">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG175">
         <v>0</v>
@@ -22571,10 +22571,10 @@
         <v>MAS DE 120 D</v>
       </c>
       <c r="AE176">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF176">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG176">
         <v>0</v>
@@ -22693,10 +22693,10 @@
         <v>MAS DE 120 D</v>
       </c>
       <c r="AE177">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF177">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG177">
         <v>0</v>
@@ -22818,10 +22818,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE178">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG178">
         <v>0</v>
@@ -22940,13 +22940,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD179" t="str">
-        <v>HASTA 60 D</v>
+        <v>HASTA 30 D</v>
       </c>
       <c r="AE179">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF179">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG179">
         <v>0</v>
@@ -23062,13 +23062,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD180" t="str">
-        <v>HASTA 60 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE180">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="AF180">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG180">
         <v>0</v>
@@ -23184,13 +23184,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD181" t="str">
-        <v>HASTA 60 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE181">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="AF181">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG181">
         <v>0</v>
@@ -23312,13 +23312,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD182" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE182">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="AF182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG182">
         <v>0</v>
@@ -23440,13 +23440,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD183" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE183">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="AF183">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG183">
         <v>0</v>
@@ -23568,13 +23568,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD184" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG184">
         <v>0</v>
@@ -23693,13 +23693,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD185" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE185">
-        <v>-28</v>
+        <v>-27</v>
       </c>
       <c r="AF185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG185">
         <v>0</v>
@@ -23824,10 +23824,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE186">
-        <v>-41</v>
+        <v>-40</v>
       </c>
       <c r="AF186">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG186">
         <v>0</v>
@@ -23949,10 +23949,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE187">
-        <v>-41</v>
+        <v>-40</v>
       </c>
       <c r="AF187">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG187">
         <v>0</v>
@@ -24074,10 +24074,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE188">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG188">
         <v>0</v>
@@ -24193,13 +24193,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD189" t="str">
-        <v>HASTA 60 D</v>
+        <v>HASTA 30 D</v>
       </c>
       <c r="AE189">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AF189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG189">
         <v>0</v>
@@ -24321,13 +24321,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD190" t="str">
-        <v>HASTA 60 D</v>
+        <v>HASTA 30 D</v>
       </c>
       <c r="AE190">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AF190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG190">
         <v>0</v>
@@ -24452,10 +24452,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE191">
-        <v>-86</v>
+        <v>-85</v>
       </c>
       <c r="AF191">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG191">
         <v>0</v>
@@ -24580,10 +24580,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE192">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG192">
         <v>0</v>
@@ -24702,10 +24702,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE193">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="AF193">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG193">
         <v>0</v>
@@ -24824,13 +24824,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD194" t="str">
-        <v>MAS DE 120 D</v>
+        <v>HASTA 30 D</v>
       </c>
       <c r="AE194">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF194">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG194">
         <v>0</v>
@@ -24952,13 +24952,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD195" t="str">
-        <v>MAS DE 120 D</v>
+        <v>HASTA 30 D</v>
       </c>
       <c r="AE195">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG195">
         <v>0</v>
@@ -25080,13 +25080,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD196" t="str">
-        <v>MAS DE 120 D</v>
+        <v>HASTA 30 D</v>
       </c>
       <c r="AE196">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF196">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG196">
         <v>0</v>
@@ -25208,13 +25208,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD197" t="str">
-        <v>MAS DE 120 D</v>
+        <v>HASTA 30 D</v>
       </c>
       <c r="AE197">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG197">
         <v>0</v>
@@ -25336,13 +25336,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD198" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE198">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="AF198">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG198">
         <v>0</v>
@@ -25464,13 +25464,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD199" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE199">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="AF199">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG199">
         <v>0</v>
@@ -25592,13 +25592,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD200" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE200">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="AF200">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG200">
         <v>0</v>
@@ -25723,13 +25723,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD201" t="str">
-        <v>HASTA 30 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE201">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="AF201">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG201">
         <v>0</v>
@@ -25854,10 +25854,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE202">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="AF202">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG202">
         <v>0</v>
@@ -25898,61 +25898,70 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B203" t="str">
-        <v>7624157-0</v>
+        <v>15145160-8</v>
       </c>
       <c r="C203" t="str">
-        <v>HERNANDEZ GRANDON LASTENIA DEL C.</v>
+        <v>ACUÑA MUÑOZ MIRIAM DEL CARMEN</v>
       </c>
       <c r="D203" t="str">
-        <v>SANTIAGO</v>
+        <v>Metropolitana</v>
+      </c>
+      <c r="E203" t="str">
+        <v>Lampa</v>
+      </c>
+      <c r="F203" t="str">
+        <v>VALLES UNIDOS CENTRO</v>
       </c>
       <c r="G203">
-        <v>1011325</v>
+        <v>1015371</v>
       </c>
       <c r="H203" t="str">
         <v>ACTIVO VALIDADO</v>
       </c>
       <c r="I203">
-        <v>97736</v>
+        <v>99778</v>
       </c>
       <c r="J203">
-        <v>2.38</v>
+        <v>99778</v>
       </c>
       <c r="K203">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="L203">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="M203" t="str">
-        <v>01/10/2026</v>
+        <v>06/10/2026</v>
       </c>
       <c r="N203">
-        <v>2.38</v>
+        <v>99778</v>
       </c>
       <c r="O203">
-        <v>97736</v>
+        <v>99778</v>
       </c>
       <c r="P203" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="Q203">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="R203">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="S203">
-        <v>41065.38</v>
+        <v>1</v>
       </c>
       <c r="T203">
-        <v>12</v>
+        <v>8</v>
+      </c>
+      <c r="U203" t="str">
+        <v>OFICINA</v>
       </c>
       <c r="V203" t="str">
         <v>Tarjetas de Debito</v>
       </c>
       <c r="W203" t="str">
-        <v>UF</v>
+        <v>PESOS</v>
       </c>
       <c r="X203" t="str">
         <v>ACARTERA1</v>
@@ -25970,19 +25979,19 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD203" t="str">
-        <v>AL DIA</v>
+        <v>HASTA 30 D</v>
       </c>
       <c r="AE203">
-        <v>-391</v>
+        <v>-26</v>
       </c>
       <c r="AF203">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AG203">
         <v>0</v>
       </c>
       <c r="AH203" t="str">
-        <v>Cuota periódica</v>
+        <v>Crédito</v>
       </c>
       <c r="AI203" t="str">
         <v>C.I.</v>
@@ -25991,22 +26000,22 @@
         <v>Cobro</v>
       </c>
       <c r="AK203">
-        <v>220600</v>
-      </c>
-      <c r="AM203">
-        <v>1194</v>
+        <v>221111</v>
+      </c>
+      <c r="AL203">
+        <v>5732</v>
       </c>
       <c r="AQ203" t="str">
-        <v>MANT 2 UF NF - PROP: 1011325 - 4-H-28</v>
+        <v>CONTRATO NRO: Valle De Las Rosas 1-AG-18</v>
       </c>
       <c r="AR203" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
+        <v>miriam2457@hotmal.com - miriam2457@hotmail.com</v>
       </c>
       <c r="AS203" t="str">
         <v/>
       </c>
       <c r="AT203" t="str">
-        <v>945718455</v>
+        <v>971986833</v>
       </c>
       <c r="AU203" t="str">
         <v>SEPULTURA</v>
@@ -26017,58 +26026,58 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B204" t="str">
-        <v>8956540-5</v>
+        <v>8557758-1</v>
       </c>
       <c r="C204" t="str">
-        <v>ELGUETA CORTEZ BERNARDITA DEL PILAR</v>
+        <v>CARRASCO PAREDES SANTIAGO PATRICIO</v>
       </c>
       <c r="D204" t="str">
         <v>SANTIAGO</v>
       </c>
-      <c r="E204" t="str">
-        <v>LOS PARQUES DE QUILICURA</v>
+      <c r="F204" t="str">
+        <v>VALLES UNIDOS CENTRO</v>
       </c>
       <c r="G204">
-        <v>1013857</v>
+        <v>1013821</v>
       </c>
       <c r="H204" t="str">
         <v>ACTIVO VALIDADO</v>
       </c>
       <c r="I204">
-        <v>97736</v>
+        <v>63715</v>
       </c>
       <c r="J204">
-        <v>2.38</v>
+        <v>1.55</v>
       </c>
       <c r="K204">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="L204">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="M204" t="str">
-        <v>01/10/2026</v>
+        <v>06/10/2026</v>
       </c>
       <c r="N204">
-        <v>0.244</v>
+        <v>1.55</v>
       </c>
       <c r="O204">
-        <v>10020</v>
+        <v>63715</v>
       </c>
       <c r="P204" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="Q204">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="R204">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="S204">
-        <v>41065.38</v>
+        <v>41106.35</v>
       </c>
       <c r="T204">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="U204" t="str">
         <v>OFICINA</v>
@@ -26101,16 +26110,16 @@
         <v>AL DIA</v>
       </c>
       <c r="AE204">
-        <v>-543</v>
+        <v>-30</v>
       </c>
       <c r="AF204">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AG204">
         <v>0</v>
       </c>
       <c r="AH204" t="str">
-        <v>Cuota periódica</v>
+        <v>Crédito</v>
       </c>
       <c r="AI204" t="str">
         <v>C.I.</v>
@@ -26119,22 +26128,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK204">
-        <v>220616</v>
-      </c>
-      <c r="AM204">
-        <v>15273</v>
+        <v>221113</v>
+      </c>
+      <c r="AL204">
+        <v>4551</v>
       </c>
       <c r="AQ204" t="str">
-        <v>MANT 2 UF NF - PROP: 1013857 - 3-E-38</v>
+        <v>Venta Inmediata VU - Familiar Ampliable PROP: 1013</v>
       </c>
       <c r="AR204" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS204" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT204" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU204" t="str">
         <v>SEPULTURA</v>
@@ -26145,16 +26151,16 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B205" t="str">
-        <v>6116830-3</v>
+        <v>7624157-0</v>
       </c>
       <c r="C205" t="str">
-        <v>VALENZUELA GONZALEZ LUIS ERASMO</v>
+        <v>HERNANDEZ GRANDON LASTENIA DEL C.</v>
       </c>
       <c r="D205" t="str">
         <v>SANTIAGO</v>
       </c>
       <c r="G205">
-        <v>1014341</v>
+        <v>1011325</v>
       </c>
       <c r="H205" t="str">
         <v>ACTIVO VALIDADO</v>
@@ -26166,10 +26172,10 @@
         <v>2.38</v>
       </c>
       <c r="K205">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L205">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M205" t="str">
         <v>01/10/2026</v>
@@ -26184,34 +26190,34 @@
         <v>SIN DATOS</v>
       </c>
       <c r="Q205">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R205">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="S205">
         <v>41065.38</v>
       </c>
       <c r="T205">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="V205" t="str">
-        <v>Tarjetas de Credito</v>
+        <v>Tarjetas de Debito</v>
       </c>
       <c r="W205" t="str">
         <v>UF</v>
       </c>
       <c r="X205" t="str">
-        <v>AVerdugo</v>
+        <v>ACARTERA1</v>
       </c>
       <c r="Y205" t="str">
-        <v>AVerdugo</v>
+        <v>ACARTERA1</v>
       </c>
       <c r="Z205" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="AB205" t="str">
-        <v>CajaParque</v>
+        <v>CajaLider</v>
       </c>
       <c r="AC205" t="str">
         <v>SIN DATOS</v>
@@ -26220,10 +26226,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE205">
-        <v>-56</v>
+        <v>-390</v>
       </c>
       <c r="AF205">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG205">
         <v>0</v>
@@ -26238,22 +26244,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK205">
-        <v>220662</v>
+        <v>220600</v>
       </c>
       <c r="AM205">
-        <v>16231</v>
+        <v>1194</v>
       </c>
       <c r="AQ205" t="str">
-        <v>MANT 2 UF NF - PROP: 1014341 - 1-M-15</v>
+        <v>MANT 2 UF NF - PROP: 1011325 - 4-H-28</v>
       </c>
       <c r="AR205" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS205" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT205" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU205" t="str">
         <v>SEPULTURA</v>
@@ -26264,16 +26267,19 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B206" t="str">
-        <v>9409740-1</v>
+        <v>8956540-5</v>
       </c>
       <c r="C206" t="str">
-        <v>PIZARRO MORALES ALICIA ELIZABETH</v>
+        <v>ELGUETA CORTEZ BERNARDITA DEL PILAR</v>
       </c>
       <c r="D206" t="str">
         <v>SANTIAGO</v>
       </c>
+      <c r="E206" t="str">
+        <v>LOS PARQUES DE QUILICURA</v>
+      </c>
       <c r="G206">
-        <v>1011704</v>
+        <v>1013857</v>
       </c>
       <c r="H206" t="str">
         <v>ACTIVO VALIDADO</v>
@@ -26285,34 +26291,37 @@
         <v>2.38</v>
       </c>
       <c r="K206">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L206">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M206" t="str">
         <v>01/10/2026</v>
       </c>
       <c r="N206">
-        <v>2.38</v>
+        <v>0.244</v>
       </c>
       <c r="O206">
-        <v>97736</v>
+        <v>10020</v>
       </c>
       <c r="P206" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="Q206">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R206">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="S206">
         <v>41065.38</v>
       </c>
       <c r="T206">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="U206" t="str">
+        <v>OFICINA</v>
       </c>
       <c r="V206" t="str">
         <v>Tarjetas de Debito</v>
@@ -26321,16 +26330,19 @@
         <v>UF</v>
       </c>
       <c r="X206" t="str">
-        <v>AVerdugo</v>
+        <v>ACARTERA1</v>
       </c>
       <c r="Y206" t="str">
-        <v>AVerdugo</v>
+        <v>ACARTERA1</v>
       </c>
       <c r="Z206" t="str">
         <v>SIN DATOS</v>
       </c>
+      <c r="AA206" t="str">
+        <v>ALBANY JASPE</v>
+      </c>
       <c r="AB206" t="str">
-        <v>CajaParque</v>
+        <v>CajaLider</v>
       </c>
       <c r="AC206" t="str">
         <v>SIN DATOS</v>
@@ -26339,10 +26351,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE206">
-        <v>-360</v>
+        <v>-542</v>
       </c>
       <c r="AF206">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG206">
         <v>0</v>
@@ -26357,22 +26369,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK206">
-        <v>220670</v>
+        <v>220616</v>
       </c>
       <c r="AM206">
-        <v>2027</v>
+        <v>15273</v>
       </c>
       <c r="AQ206" t="str">
-        <v>MANT 2 UF NF - PROP: 1011704 - 5-N-50</v>
+        <v>MANT 2 UF NF - PROP: 1013857 - 3-E-38</v>
       </c>
       <c r="AR206" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS206" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT206" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU206" t="str">
         <v>SEPULTURA</v>
@@ -26383,73 +26392,73 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B207" t="str">
-        <v>11249083-3</v>
+        <v>6116830-3</v>
       </c>
       <c r="C207" t="str">
-        <v>NAVARRETE AGUILAR PATRICIA DEL CARMEN</v>
+        <v>VALENZUELA GONZALEZ LUIS ERASMO</v>
       </c>
       <c r="D207" t="str">
         <v>SANTIAGO</v>
       </c>
       <c r="G207">
-        <v>1011321</v>
+        <v>1014341</v>
       </c>
       <c r="H207" t="str">
         <v>ACTIVO VALIDADO</v>
       </c>
       <c r="I207">
-        <v>97755</v>
+        <v>97736</v>
       </c>
       <c r="J207">
         <v>2.38</v>
       </c>
       <c r="K207">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="L207">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M207" t="str">
-        <v>02/10/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="N207">
         <v>2.38</v>
       </c>
       <c r="O207">
-        <v>97755</v>
+        <v>97736</v>
       </c>
       <c r="P207" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="Q207">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R207">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="S207">
-        <v>41073.57</v>
+        <v>41065.38</v>
       </c>
       <c r="T207">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="V207" t="str">
-        <v>Tarjetas de Debito</v>
+        <v>Tarjetas de Credito</v>
       </c>
       <c r="W207" t="str">
         <v>UF</v>
       </c>
       <c r="X207" t="str">
-        <v>ACARTERA1</v>
+        <v>AVerdugo</v>
       </c>
       <c r="Y207" t="str">
-        <v>ACARTERA1</v>
+        <v>AVerdugo</v>
       </c>
       <c r="Z207" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="AB207" t="str">
-        <v>CajaLider</v>
+        <v>CajaParque</v>
       </c>
       <c r="AC207" t="str">
         <v>SIN DATOS</v>
@@ -26458,10 +26467,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE207">
-        <v>-391</v>
+        <v>-55</v>
       </c>
       <c r="AF207">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG207">
         <v>0</v>
@@ -26476,22 +26485,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK207">
-        <v>220701</v>
+        <v>220662</v>
       </c>
       <c r="AM207">
-        <v>1185</v>
+        <v>16231</v>
       </c>
       <c r="AQ207" t="str">
-        <v>MANT 2 UF NF - PROP: 1011321 - 3-AW-22</v>
+        <v>MANT 2 UF NF - PROP: 1014341 - 1-M-15</v>
       </c>
       <c r="AR207" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS207" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT207" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU207" t="str">
         <v>SEPULTURA</v>
@@ -26502,43 +26508,40 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B208" t="str">
-        <v>12553530-5</v>
+        <v>9409740-1</v>
       </c>
       <c r="C208" t="str">
-        <v>SANCHEZ SOTO  CLAUDIA ANDREA</v>
+        <v>PIZARRO MORALES ALICIA ELIZABETH</v>
       </c>
       <c r="D208" t="str">
-        <v>Metropolitana</v>
-      </c>
-      <c r="E208" t="str">
-        <v>Renca</v>
+        <v>SANTIAGO</v>
       </c>
       <c r="G208">
-        <v>1013944</v>
+        <v>1011704</v>
       </c>
       <c r="H208" t="str">
         <v>ACTIVO VALIDADO</v>
       </c>
       <c r="I208">
-        <v>97755</v>
+        <v>97736</v>
       </c>
       <c r="J208">
         <v>2.38</v>
       </c>
       <c r="K208">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L208">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M208" t="str">
-        <v>02/10/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="N208">
         <v>2.38</v>
       </c>
       <c r="O208">
-        <v>97755</v>
+        <v>97736</v>
       </c>
       <c r="P208" t="str">
         <v>SIN DATOS</v>
@@ -26547,16 +26550,13 @@
         <v>4</v>
       </c>
       <c r="R208">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="S208">
-        <v>41073.57</v>
+        <v>41065.38</v>
       </c>
       <c r="T208">
-        <v>1</v>
-      </c>
-      <c r="U208" t="str">
-        <v>OFICINA</v>
+        <v>11</v>
       </c>
       <c r="V208" t="str">
         <v>Tarjetas de Debito</v>
@@ -26573,9 +26573,6 @@
       <c r="Z208" t="str">
         <v>SIN DATOS</v>
       </c>
-      <c r="AA208" t="str">
-        <v>ALBANY JASPE</v>
-      </c>
       <c r="AB208" t="str">
         <v>CajaParque</v>
       </c>
@@ -26586,10 +26583,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE208">
-        <v>-299</v>
+        <v>-359</v>
       </c>
       <c r="AF208">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG208">
         <v>0</v>
@@ -26604,22 +26601,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK208">
-        <v>220741</v>
+        <v>220670</v>
       </c>
       <c r="AM208">
-        <v>15448</v>
+        <v>2027</v>
       </c>
       <c r="AQ208" t="str">
-        <v>MANT 2 UF NF - PROP: 1013944 - 2-F-13</v>
+        <v>MANT 2 UF NF - PROP: 1011704 - 5-N-50</v>
       </c>
       <c r="AR208" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS208" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT208" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU208" t="str">
         <v>SEPULTURA</v>
@@ -26630,40 +26624,40 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B209" t="str">
-        <v>16373042-1</v>
+        <v>11249083-3</v>
       </c>
       <c r="C209" t="str">
-        <v>HERNANDEZ RUIZ GERALDINA ELIANA</v>
+        <v>NAVARRETE AGUILAR PATRICIA DEL CARMEN</v>
       </c>
       <c r="D209" t="str">
         <v>SANTIAGO</v>
       </c>
       <c r="G209">
-        <v>1013002</v>
+        <v>1011321</v>
       </c>
       <c r="H209" t="str">
         <v>ACTIVO VALIDADO</v>
       </c>
       <c r="I209">
-        <v>97736</v>
+        <v>97755</v>
       </c>
       <c r="J209">
         <v>2.38</v>
       </c>
       <c r="K209">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L209">
         <v>31</v>
       </c>
       <c r="M209" t="str">
-        <v>01/10/2026</v>
+        <v>02/10/2026</v>
       </c>
       <c r="N209">
         <v>2.38</v>
       </c>
       <c r="O209">
-        <v>97736</v>
+        <v>97755</v>
       </c>
       <c r="P209" t="str">
         <v>SIN DATOS</v>
@@ -26672,16 +26666,16 @@
         <v>4</v>
       </c>
       <c r="R209">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S209">
-        <v>41065.38</v>
+        <v>41073.57</v>
       </c>
       <c r="T209">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="V209" t="str">
-        <v>BANCO ESTADO</v>
+        <v>Tarjetas de Debito</v>
       </c>
       <c r="W209" t="str">
         <v>UF</v>
@@ -26705,7 +26699,7 @@
         <v>AL DIA</v>
       </c>
       <c r="AE209">
-        <v>-330</v>
+        <v>-390</v>
       </c>
       <c r="AF209">
         <v>4</v>
@@ -26723,22 +26717,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK209">
-        <v>220745</v>
+        <v>220701</v>
       </c>
       <c r="AM209">
-        <v>13450</v>
+        <v>1185</v>
       </c>
       <c r="AQ209" t="str">
-        <v>MANT 2 UF NI - PROP: 1013002 - 2-U-18</v>
+        <v>MANT 2 UF NF - PROP: 1011321 - 3-AW-22</v>
       </c>
       <c r="AR209" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS209" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT209" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU209" t="str">
         <v>SEPULTURA</v>
@@ -26749,19 +26740,19 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B210" t="str">
-        <v>16862217-1</v>
+        <v>12553530-5</v>
       </c>
       <c r="C210" t="str">
-        <v>FARIAS CARO SERGIO ALEJANDRO</v>
+        <v>SANCHEZ SOTO  CLAUDIA ANDREA</v>
       </c>
       <c r="D210" t="str">
         <v>Metropolitana</v>
       </c>
       <c r="E210" t="str">
-        <v>La Cisterna</v>
+        <v>Renca</v>
       </c>
       <c r="G210">
-        <v>1012614</v>
+        <v>1013944</v>
       </c>
       <c r="H210" t="str">
         <v>ACTIVO VALIDADO</v>
@@ -26773,10 +26764,10 @@
         <v>2.38</v>
       </c>
       <c r="K210">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L210">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M210" t="str">
         <v>02/10/2026</v>
@@ -26791,46 +26782,52 @@
         <v>SIN DATOS</v>
       </c>
       <c r="Q210">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R210">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S210">
         <v>41073.57</v>
       </c>
       <c r="T210">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="U210" t="str">
+        <v>OFICINA</v>
       </c>
       <c r="V210" t="str">
-        <v>BANCO ESTADO</v>
+        <v>Tarjetas de Debito</v>
       </c>
       <c r="W210" t="str">
         <v>UF</v>
       </c>
       <c r="X210" t="str">
-        <v>ACARTERA1</v>
+        <v>AVerdugo</v>
       </c>
       <c r="Y210" t="str">
-        <v>ACARTERA1</v>
+        <v>AVerdugo</v>
       </c>
       <c r="Z210" t="str">
         <v>SIN DATOS</v>
       </c>
+      <c r="AA210" t="str">
+        <v>ALBANY JASPE</v>
+      </c>
       <c r="AB210" t="str">
-        <v>CajaLider</v>
+        <v>CajaParque</v>
       </c>
       <c r="AC210" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="AD210" t="str">
-        <v>MAS DE 120 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE210">
-        <v>735</v>
+        <v>-298</v>
       </c>
       <c r="AF210">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG210">
         <v>0</v>
@@ -26845,22 +26842,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK210">
-        <v>220776</v>
+        <v>220741</v>
       </c>
       <c r="AM210">
-        <v>12591</v>
+        <v>15448</v>
       </c>
       <c r="AQ210" t="str">
-        <v>MANT 2 UF NF - PROP: 1012614 - 2-D-14</v>
+        <v>MANT 2 UF NF - PROP: 1013944 - 2-F-13</v>
       </c>
       <c r="AR210" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS210" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT210" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU210" t="str">
         <v>SEPULTURA</v>
@@ -26871,58 +26865,55 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B211" t="str">
-        <v>16862217-1</v>
+        <v>16373042-1</v>
       </c>
       <c r="C211" t="str">
-        <v>FARIAS CARO SERGIO ALEJANDRO</v>
+        <v>HERNANDEZ RUIZ GERALDINA ELIANA</v>
       </c>
       <c r="D211" t="str">
-        <v>Metropolitana</v>
-      </c>
-      <c r="E211" t="str">
-        <v>La Cisterna</v>
+        <v>SANTIAGO</v>
       </c>
       <c r="G211">
-        <v>1012614</v>
+        <v>1013002</v>
       </c>
       <c r="H211" t="str">
         <v>ACTIVO VALIDADO</v>
       </c>
       <c r="I211">
-        <v>97755</v>
+        <v>97736</v>
       </c>
       <c r="J211">
         <v>2.38</v>
       </c>
       <c r="K211">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L211">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M211" t="str">
-        <v>02/10/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="N211">
-        <v>1.272</v>
+        <v>2.38</v>
       </c>
       <c r="O211">
-        <v>52246</v>
+        <v>97736</v>
       </c>
       <c r="P211" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="Q211">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R211">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S211">
-        <v>41073.57</v>
+        <v>41065.38</v>
       </c>
       <c r="T211">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V211" t="str">
         <v>BANCO ESTADO</v>
@@ -26946,13 +26937,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD211" t="str">
-        <v>MAS DE 120 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE211">
-        <v>735</v>
+        <v>-329</v>
       </c>
       <c r="AF211">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG211">
         <v>0</v>
@@ -26967,22 +26958,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK211">
-        <v>220776</v>
+        <v>220745</v>
       </c>
       <c r="AM211">
-        <v>12591</v>
+        <v>13450</v>
       </c>
       <c r="AQ211" t="str">
-        <v>MANT 2 UF NF - PROP: 1012614 - 2-D-14</v>
+        <v>MANT 2 UF NI - PROP: 1013002 - 2-U-18</v>
       </c>
       <c r="AR211" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS211" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT211" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU211" t="str">
         <v>SEPULTURA</v>
@@ -26993,16 +26981,19 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B212" t="str">
-        <v>9774012-7</v>
+        <v>16862217-1</v>
       </c>
       <c r="C212" t="str">
-        <v>ZUÑIGA ALUCEMA RAUL DEL CARMEN</v>
+        <v>FARIAS CARO SERGIO ALEJANDRO</v>
       </c>
       <c r="D212" t="str">
-        <v>SANTIAGO</v>
+        <v>Metropolitana</v>
+      </c>
+      <c r="E212" t="str">
+        <v>La Cisterna</v>
       </c>
       <c r="G212">
-        <v>1012105</v>
+        <v>1012614</v>
       </c>
       <c r="H212" t="str">
         <v>ACTIVO VALIDADO</v>
@@ -27014,37 +27005,37 @@
         <v>2.38</v>
       </c>
       <c r="K212">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L212">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M212" t="str">
         <v>02/10/2026</v>
       </c>
       <c r="N212">
-        <v>0.487</v>
+        <v>2.38</v>
       </c>
       <c r="O212">
-        <v>20003</v>
+        <v>97755</v>
       </c>
       <c r="P212" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="Q212">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R212">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="S212">
         <v>41073.57</v>
       </c>
       <c r="T212">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V212" t="str">
-        <v>Tarjetas de Debito</v>
+        <v>BANCO ESTADO</v>
       </c>
       <c r="W212" t="str">
         <v>UF</v>
@@ -27065,13 +27056,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD212" t="str">
-        <v>HASTA 30 D</v>
+        <v>MAS DE 120 D</v>
       </c>
       <c r="AE212">
-        <v>66</v>
+        <v>736</v>
       </c>
       <c r="AF212">
-        <v>366</v>
+        <v>4</v>
       </c>
       <c r="AG212">
         <v>0</v>
@@ -27086,22 +27077,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK212">
-        <v>220831</v>
+        <v>220776</v>
       </c>
       <c r="AM212">
-        <v>11541</v>
+        <v>12591</v>
       </c>
       <c r="AQ212" t="str">
-        <v>MANT 2 UF NF - PROP: 1012105 - 5-Q-81</v>
+        <v>MANT 2 UF NF - PROP: 1012614 - 2-D-14</v>
       </c>
       <c r="AR212" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS212" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT212" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU212" t="str">
         <v>SEPULTURA</v>
@@ -27112,19 +27100,19 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B213" t="str">
-        <v>14901236-2</v>
+        <v>16862217-1</v>
       </c>
       <c r="C213" t="str">
-        <v>BRISIMONTIER GONZALEZ CARLOS JONATHAN</v>
+        <v>FARIAS CARO SERGIO ALEJANDRO</v>
       </c>
       <c r="D213" t="str">
-        <v>SANTIAGO</v>
-      </c>
-      <c r="F213" t="str">
-        <v>VALLES UNIDOS CENTRO</v>
+        <v>Metropolitana</v>
+      </c>
+      <c r="E213" t="str">
+        <v>La Cisterna</v>
       </c>
       <c r="G213">
-        <v>600</v>
+        <v>1012614</v>
       </c>
       <c r="H213" t="str">
         <v>ACTIVO VALIDADO</v>
@@ -27136,7 +27124,7 @@
         <v>2.38</v>
       </c>
       <c r="K213">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L213">
         <v>30</v>
@@ -27145,58 +27133,55 @@
         <v>02/10/2026</v>
       </c>
       <c r="N213">
-        <v>2.38</v>
+        <v>1.272</v>
       </c>
       <c r="O213">
-        <v>97755</v>
+        <v>52246</v>
       </c>
       <c r="P213" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="Q213">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R213">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S213">
         <v>41073.57</v>
       </c>
       <c r="T213">
-        <v>4</v>
-      </c>
-      <c r="U213" t="str">
-        <v>OFICINA</v>
+        <v>7</v>
       </c>
       <c r="V213" t="str">
-        <v>Tarjetas de Debito</v>
+        <v>BANCO ESTADO</v>
       </c>
       <c r="W213" t="str">
         <v>UF</v>
       </c>
       <c r="X213" t="str">
-        <v>AVerdugo</v>
+        <v>ACARTERA1</v>
       </c>
       <c r="Y213" t="str">
-        <v>AVerdugo</v>
+        <v>ACARTERA1</v>
       </c>
       <c r="Z213" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="AB213" t="str">
-        <v>CajaParque</v>
+        <v>CajaLider</v>
       </c>
       <c r="AC213" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="AD213" t="str">
-        <v>AL DIA</v>
+        <v>MAS DE 120 D</v>
       </c>
       <c r="AE213">
-        <v>-421</v>
+        <v>736</v>
       </c>
       <c r="AF213">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG213">
         <v>0</v>
@@ -27211,22 +27196,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK213">
-        <v>220838</v>
+        <v>220776</v>
       </c>
       <c r="AM213">
-        <v>10600</v>
+        <v>12591</v>
       </c>
       <c r="AQ213" t="str">
-        <v>MANTENIMIENTO 2.000 UF</v>
+        <v>MANT 2 UF NF - PROP: 1012614 - 2-D-14</v>
       </c>
       <c r="AR213" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS213" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT213" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU213" t="str">
         <v>SEPULTURA</v>
@@ -27237,64 +27219,58 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B214" t="str">
-        <v>11320998-4</v>
+        <v>9774012-7</v>
       </c>
       <c r="C214" t="str">
-        <v>CASTRO URRA URRA JOSE ANTONIO ORLANDO</v>
+        <v>ZUÑIGA ALUCEMA RAUL DEL CARMEN</v>
       </c>
       <c r="D214" t="str">
         <v>SANTIAGO</v>
       </c>
-      <c r="F214" t="str">
-        <v>VALLES UNIDOS CENTRO</v>
-      </c>
       <c r="G214">
-        <v>85</v>
+        <v>1012105</v>
       </c>
       <c r="H214" t="str">
         <v>ACTIVO VALIDADO</v>
       </c>
       <c r="I214">
-        <v>97775</v>
+        <v>97755</v>
       </c>
       <c r="J214">
         <v>2.38</v>
       </c>
       <c r="K214">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L214">
         <v>31</v>
       </c>
       <c r="M214" t="str">
-        <v>03/10/2026</v>
+        <v>02/10/2026</v>
       </c>
       <c r="N214">
-        <v>2.38</v>
+        <v>0.487</v>
       </c>
       <c r="O214">
-        <v>97775</v>
+        <v>20003</v>
       </c>
       <c r="P214" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="Q214">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R214">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="S214">
-        <v>41081.76</v>
+        <v>41073.57</v>
       </c>
       <c r="T214">
-        <v>14</v>
-      </c>
-      <c r="U214" t="str">
-        <v>OFICINA</v>
+        <v>10</v>
       </c>
       <c r="V214" t="str">
-        <v>EFECTIVO</v>
+        <v>Tarjetas de Debito</v>
       </c>
       <c r="W214" t="str">
         <v>UF</v>
@@ -27308,9 +27284,6 @@
       <c r="Z214" t="str">
         <v>SIN DATOS</v>
       </c>
-      <c r="AA214" t="str">
-        <v>SIKIU AVENDAÑO</v>
-      </c>
       <c r="AB214" t="str">
         <v>CajaLider</v>
       </c>
@@ -27321,10 +27294,10 @@
         <v>HASTA 30 D</v>
       </c>
       <c r="AE214">
-        <v>-299</v>
+        <v>67</v>
       </c>
       <c r="AF214">
-        <v>426</v>
+        <v>367</v>
       </c>
       <c r="AG214">
         <v>0</v>
@@ -27339,22 +27312,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK214">
-        <v>220853</v>
+        <v>220831</v>
       </c>
       <c r="AM214">
-        <v>10085</v>
+        <v>11541</v>
       </c>
       <c r="AQ214" t="str">
-        <v>MANTENIMIENTO 2.000 UF</v>
+        <v>MANT 2 UF NF - PROP: 1012105 - 5-Q-81</v>
       </c>
       <c r="AR214" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS214" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT214" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU214" t="str">
         <v>SEPULTURA</v>
@@ -27365,55 +27335,61 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B215" t="str">
-        <v>10302120-0</v>
+        <v>14901236-2</v>
       </c>
       <c r="C215" t="str">
-        <v>BRIONES REQUERIN PATRICIA ROSA</v>
+        <v>BRISIMONTIER GONZALEZ CARLOS JONATHAN</v>
       </c>
       <c r="D215" t="str">
         <v>SANTIAGO</v>
       </c>
+      <c r="F215" t="str">
+        <v>VALLES UNIDOS CENTRO</v>
+      </c>
       <c r="G215">
-        <v>1013721</v>
+        <v>600</v>
       </c>
       <c r="H215" t="str">
         <v>ACTIVO VALIDADO</v>
       </c>
       <c r="I215">
-        <v>97775</v>
+        <v>97755</v>
       </c>
       <c r="J215">
         <v>2.38</v>
       </c>
       <c r="K215">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L215">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M215" t="str">
-        <v>03/10/2026</v>
+        <v>02/10/2026</v>
       </c>
       <c r="N215">
-        <v>0.365</v>
+        <v>2.38</v>
       </c>
       <c r="O215">
-        <v>14995</v>
+        <v>97755</v>
       </c>
       <c r="P215" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="Q215">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R215">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S215">
-        <v>41081.76</v>
+        <v>41073.57</v>
       </c>
       <c r="T215">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="U215" t="str">
+        <v>OFICINA</v>
       </c>
       <c r="V215" t="str">
         <v>Tarjetas de Debito</v>
@@ -27422,19 +27398,16 @@
         <v>UF</v>
       </c>
       <c r="X215" t="str">
-        <v>ACARTERA1</v>
+        <v>AVerdugo</v>
       </c>
       <c r="Y215" t="str">
-        <v>ACARTERA1</v>
+        <v>AVerdugo</v>
       </c>
       <c r="Z215" t="str">
         <v>SIN DATOS</v>
       </c>
-      <c r="AA215" t="str">
-        <v>ALBANY JASPE</v>
-      </c>
       <c r="AB215" t="str">
-        <v>CajaLider</v>
+        <v>CajaParque</v>
       </c>
       <c r="AC215" t="str">
         <v>SIN DATOS</v>
@@ -27443,10 +27416,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE215">
-        <v>35</v>
+        <v>-420</v>
       </c>
       <c r="AF215">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="AG215">
         <v>0</v>
@@ -27461,22 +27434,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK215">
-        <v>220861</v>
+        <v>220838</v>
       </c>
       <c r="AM215">
-        <v>15000</v>
+        <v>10600</v>
       </c>
       <c r="AQ215" t="str">
-        <v>MANT 2 UF NF - PROP: 1013721 - 4-H-34</v>
+        <v>MANTENIMIENTO 2.000 UF</v>
       </c>
       <c r="AR215" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS215" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT215" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU215" t="str">
         <v>SEPULTURA</v>
@@ -27487,16 +27457,19 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B216" t="str">
-        <v>11939088-5</v>
+        <v>11320998-4</v>
       </c>
       <c r="C216" t="str">
-        <v>ROJAS ESCOBAR NANCY DEL ROSARIO</v>
+        <v>CASTRO URRA URRA JOSE ANTONIO ORLANDO</v>
       </c>
       <c r="D216" t="str">
         <v>SANTIAGO</v>
       </c>
+      <c r="F216" t="str">
+        <v>VALLES UNIDOS CENTRO</v>
+      </c>
       <c r="G216">
-        <v>101027</v>
+        <v>85</v>
       </c>
       <c r="H216" t="str">
         <v>ACTIVO VALIDADO</v>
@@ -27508,7 +27481,7 @@
         <v>2.38</v>
       </c>
       <c r="K216">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L216">
         <v>31</v>
@@ -27529,16 +27502,19 @@
         <v>4</v>
       </c>
       <c r="R216">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S216">
         <v>41081.76</v>
       </c>
       <c r="T216">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="U216" t="str">
+        <v>OFICINA</v>
       </c>
       <c r="V216" t="str">
-        <v>Tarjetas de Debito</v>
+        <v>EFECTIVO</v>
       </c>
       <c r="W216" t="str">
         <v>UF</v>
@@ -27552,6 +27528,9 @@
       <c r="Z216" t="str">
         <v>SIN DATOS</v>
       </c>
+      <c r="AA216" t="str">
+        <v>SIKIU AVENDAÑO</v>
+      </c>
       <c r="AB216" t="str">
         <v>CajaLider</v>
       </c>
@@ -27559,13 +27538,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD216" t="str">
-        <v>AL DIA</v>
+        <v>HASTA 30 D</v>
       </c>
       <c r="AE216">
-        <v>-391</v>
+        <v>-298</v>
       </c>
       <c r="AF216">
-        <v>2</v>
+        <v>427</v>
       </c>
       <c r="AG216">
         <v>0</v>
@@ -27580,22 +27559,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK216">
-        <v>220865</v>
+        <v>220853</v>
       </c>
       <c r="AM216">
-        <v>522</v>
+        <v>10085</v>
       </c>
       <c r="AQ216" t="str">
-        <v>MANT 2 UF NF - PROP: 101027 - 3-P-22</v>
+        <v>MANTENIMIENTO 2.000 UF</v>
       </c>
       <c r="AR216" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS216" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT216" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU216" t="str">
         <v>SEPULTURA</v>
@@ -27606,16 +27582,16 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B217" t="str">
-        <v>14585552-7</v>
+        <v>10302120-0</v>
       </c>
       <c r="C217" t="str">
-        <v>GUAJARDO OLMEDO MARIA CECILIA</v>
+        <v>BRIONES REQUERIN PATRICIA ROSA</v>
       </c>
       <c r="D217" t="str">
         <v>SANTIAGO</v>
       </c>
       <c r="G217">
-        <v>1013704</v>
+        <v>1013721</v>
       </c>
       <c r="H217" t="str">
         <v>ACTIVO VALIDADO</v>
@@ -27636,16 +27612,16 @@
         <v>03/10/2026</v>
       </c>
       <c r="N217">
-        <v>2.38</v>
+        <v>0.365</v>
       </c>
       <c r="O217">
-        <v>97775</v>
+        <v>14995</v>
       </c>
       <c r="P217" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="Q217">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R217">
         <v>1</v>
@@ -27656,11 +27632,8 @@
       <c r="T217">
         <v>1</v>
       </c>
-      <c r="U217" t="str">
-        <v>OFICINA</v>
-      </c>
       <c r="V217" t="str">
-        <v>Tarjetas de Credito</v>
+        <v>Tarjetas de Debito</v>
       </c>
       <c r="W217" t="str">
         <v>UF</v>
@@ -27687,10 +27660,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE217">
-        <v>-330</v>
+        <v>36</v>
       </c>
       <c r="AF217">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AG217">
         <v>0</v>
@@ -27705,22 +27678,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK217">
-        <v>220875</v>
+        <v>220861</v>
       </c>
       <c r="AM217">
-        <v>14964</v>
+        <v>15000</v>
       </c>
       <c r="AQ217" t="str">
-        <v>MANT 2 UF NF - PROP: 1013704 - 4-L-21</v>
+        <v>MANT 2 UF NF - PROP: 1013721 - 4-H-34</v>
       </c>
       <c r="AR217" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS217" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT217" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU217" t="str">
         <v>SEPULTURA</v>
@@ -27731,16 +27701,16 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B218" t="str">
-        <v>15709301-0</v>
+        <v>11939088-5</v>
       </c>
       <c r="C218" t="str">
-        <v>GUAJARDO OLMEDO JOHAN ANDRES</v>
+        <v>ROJAS ESCOBAR NANCY DEL ROSARIO</v>
       </c>
       <c r="D218" t="str">
         <v>SANTIAGO</v>
       </c>
       <c r="G218">
-        <v>1013703</v>
+        <v>101027</v>
       </c>
       <c r="H218" t="str">
         <v>ACTIVO VALIDADO</v>
@@ -27752,7 +27722,7 @@
         <v>2.38</v>
       </c>
       <c r="K218">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="L218">
         <v>31</v>
@@ -27773,19 +27743,16 @@
         <v>4</v>
       </c>
       <c r="R218">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="S218">
         <v>41081.76</v>
       </c>
       <c r="T218">
-        <v>1</v>
-      </c>
-      <c r="U218" t="str">
-        <v>OFICINA</v>
+        <v>13</v>
       </c>
       <c r="V218" t="str">
-        <v>Tarjetas de Credito</v>
+        <v>Tarjetas de Debito</v>
       </c>
       <c r="W218" t="str">
         <v>UF</v>
@@ -27799,9 +27766,6 @@
       <c r="Z218" t="str">
         <v>SIN DATOS</v>
       </c>
-      <c r="AA218" t="str">
-        <v>ALBANY JASPE</v>
-      </c>
       <c r="AB218" t="str">
         <v>CajaLider</v>
       </c>
@@ -27812,10 +27776,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE218">
-        <v>-330</v>
+        <v>-390</v>
       </c>
       <c r="AF218">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG218">
         <v>0</v>
@@ -27830,22 +27794,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK218">
-        <v>220877</v>
+        <v>220865</v>
       </c>
       <c r="AM218">
-        <v>14962</v>
+        <v>522</v>
       </c>
       <c r="AQ218" t="str">
-        <v>MANT 2 UF NF - PROP: 1013703 - 4-K-21</v>
+        <v>MANT 2 UF NF - PROP: 101027 - 3-P-22</v>
       </c>
       <c r="AR218" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS218" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT218" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU218" t="str">
         <v>SEPULTURA</v>
@@ -27856,16 +27817,16 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B219" t="str">
-        <v>11486159-6</v>
+        <v>14585552-7</v>
       </c>
       <c r="C219" t="str">
-        <v>MIRANDA BARROS ALEJANDRO HERACLITO</v>
+        <v>GUAJARDO OLMEDO MARIA CECILIA</v>
       </c>
       <c r="D219" t="str">
         <v>SANTIAGO</v>
       </c>
       <c r="G219">
-        <v>1013716</v>
+        <v>1013704</v>
       </c>
       <c r="H219" t="str">
         <v>ACTIVO VALIDADO</v>
@@ -27937,10 +27898,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE219">
-        <v>-330</v>
+        <v>-329</v>
       </c>
       <c r="AF219">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG219">
         <v>0</v>
@@ -27955,22 +27916,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK219">
-        <v>220895</v>
+        <v>220875</v>
       </c>
       <c r="AM219">
-        <v>14988</v>
+        <v>14964</v>
       </c>
       <c r="AQ219" t="str">
-        <v>MANT 2 UF NF - PROP: 1013716 - 4-G-33</v>
+        <v>MANT 2 UF NF - PROP: 1013704 - 4-L-21</v>
       </c>
       <c r="AR219" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS219" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT219" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU219" t="str">
         <v>SEPULTURA</v>
@@ -27981,19 +27939,16 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B220" t="str">
-        <v>8675228-K</v>
+        <v>15709301-0</v>
       </c>
       <c r="C220" t="str">
-        <v>ESPINOZA MUNOZ MUNOZ CELIA NATIVIDAD</v>
+        <v>GUAJARDO OLMEDO JOHAN ANDRES</v>
       </c>
       <c r="D220" t="str">
         <v>SANTIAGO</v>
       </c>
-      <c r="F220" t="str">
-        <v>VALLES UNIDOS CENTRO</v>
-      </c>
       <c r="G220">
-        <v>724</v>
+        <v>1013703</v>
       </c>
       <c r="H220" t="str">
         <v>ACTIVO VALIDADO</v>
@@ -28005,7 +27960,7 @@
         <v>2.38</v>
       </c>
       <c r="K220">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="L220">
         <v>31</v>
@@ -28026,19 +27981,19 @@
         <v>4</v>
       </c>
       <c r="R220">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="S220">
         <v>41081.76</v>
       </c>
       <c r="T220">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="U220" t="str">
         <v>OFICINA</v>
       </c>
       <c r="V220" t="str">
-        <v>Tarjetas de Debito</v>
+        <v>Tarjetas de Credito</v>
       </c>
       <c r="W220" t="str">
         <v>UF</v>
@@ -28053,7 +28008,7 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AA220" t="str">
-        <v>SIKIU AVENDAÑO</v>
+        <v>ALBANY JASPE</v>
       </c>
       <c r="AB220" t="str">
         <v>CajaLider</v>
@@ -28065,10 +28020,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE220">
-        <v>-177</v>
+        <v>-329</v>
       </c>
       <c r="AF220">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG220">
         <v>0</v>
@@ -28083,22 +28038,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK220">
-        <v>220899</v>
+        <v>220877</v>
       </c>
       <c r="AM220">
-        <v>10724</v>
+        <v>14962</v>
       </c>
       <c r="AQ220" t="str">
-        <v>MANTENIMIENTO 2.000 UF</v>
+        <v>MANT 2 UF NF - PROP: 1013703 - 4-K-21</v>
       </c>
       <c r="AR220" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS220" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT220" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU220" t="str">
         <v>SEPULTURA</v>
@@ -28109,40 +28061,40 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B221" t="str">
-        <v>10840340-3</v>
+        <v>11486159-6</v>
       </c>
       <c r="C221" t="str">
-        <v>PARRA LEFIÑANCO MARIA MERCEDES</v>
+        <v>MIRANDA BARROS ALEJANDRO HERACLITO</v>
       </c>
       <c r="D221" t="str">
         <v>SANTIAGO</v>
       </c>
       <c r="G221">
-        <v>1013130</v>
+        <v>1013716</v>
       </c>
       <c r="H221" t="str">
         <v>ACTIVO VALIDADO</v>
       </c>
       <c r="I221">
-        <v>97794</v>
+        <v>97775</v>
       </c>
       <c r="J221">
         <v>2.38</v>
       </c>
       <c r="K221">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L221">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M221" t="str">
-        <v>04/10/2026</v>
+        <v>03/10/2026</v>
       </c>
       <c r="N221">
-        <v>1.153</v>
+        <v>2.38</v>
       </c>
       <c r="O221">
-        <v>47377</v>
+        <v>97775</v>
       </c>
       <c r="P221" t="str">
         <v>SIN DATOS</v>
@@ -28151,31 +28103,37 @@
         <v>4</v>
       </c>
       <c r="R221">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S221">
-        <v>41089.96</v>
+        <v>41081.76</v>
       </c>
       <c r="T221">
-        <v>7</v>
+        <v>1</v>
+      </c>
+      <c r="U221" t="str">
+        <v>OFICINA</v>
       </c>
       <c r="V221" t="str">
-        <v>Tarjetas de Debito</v>
+        <v>Tarjetas de Credito</v>
       </c>
       <c r="W221" t="str">
         <v>UF</v>
       </c>
       <c r="X221" t="str">
-        <v>AVerdugo</v>
+        <v>ACARTERA1</v>
       </c>
       <c r="Y221" t="str">
-        <v>AVerdugo</v>
+        <v>ACARTERA1</v>
       </c>
       <c r="Z221" t="str">
         <v>SIN DATOS</v>
       </c>
+      <c r="AA221" t="str">
+        <v>ALBANY JASPE</v>
+      </c>
       <c r="AB221" t="str">
-        <v>CajaParque</v>
+        <v>CajaLider</v>
       </c>
       <c r="AC221" t="str">
         <v>SIN DATOS</v>
@@ -28184,10 +28142,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE221">
-        <v>-360</v>
+        <v>-329</v>
       </c>
       <c r="AF221">
-        <v>361</v>
+        <v>3</v>
       </c>
       <c r="AG221">
         <v>0</v>
@@ -28202,22 +28160,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK221">
-        <v>220938</v>
+        <v>220895</v>
       </c>
       <c r="AM221">
-        <v>13760</v>
+        <v>14988</v>
       </c>
       <c r="AQ221" t="str">
-        <v>MANT 2 UF NF - PROP: 1013130 - 1-AF-17</v>
+        <v>MANT 2 UF NF - PROP: 1013716 - 4-G-33</v>
       </c>
       <c r="AR221" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS221" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT221" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU221" t="str">
         <v>SEPULTURA</v>
@@ -28228,40 +28183,43 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B222" t="str">
-        <v>10840340-3</v>
+        <v>8675228-K</v>
       </c>
       <c r="C222" t="str">
-        <v>PARRA LEFIÑANCO MARIA MERCEDES</v>
+        <v>ESPINOZA MUNOZ MUNOZ CELIA NATIVIDAD</v>
       </c>
       <c r="D222" t="str">
         <v>SANTIAGO</v>
       </c>
+      <c r="F222" t="str">
+        <v>VALLES UNIDOS CENTRO</v>
+      </c>
       <c r="G222">
-        <v>1013130</v>
+        <v>724</v>
       </c>
       <c r="H222" t="str">
         <v>ACTIVO VALIDADO</v>
       </c>
       <c r="I222">
-        <v>97794</v>
+        <v>97775</v>
       </c>
       <c r="J222">
         <v>2.38</v>
       </c>
       <c r="K222">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L222">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M222" t="str">
-        <v>04/10/2026</v>
+        <v>03/10/2026</v>
       </c>
       <c r="N222">
-        <v>1.153</v>
+        <v>2.38</v>
       </c>
       <c r="O222">
-        <v>47377</v>
+        <v>97775</v>
       </c>
       <c r="P222" t="str">
         <v>SIN DATOS</v>
@@ -28270,13 +28228,16 @@
         <v>4</v>
       </c>
       <c r="R222">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="S222">
-        <v>41089.96</v>
+        <v>41081.76</v>
       </c>
       <c r="T222">
-        <v>7</v>
+        <v>13</v>
+      </c>
+      <c r="U222" t="str">
+        <v>OFICINA</v>
       </c>
       <c r="V222" t="str">
         <v>Tarjetas de Debito</v>
@@ -28285,16 +28246,19 @@
         <v>UF</v>
       </c>
       <c r="X222" t="str">
-        <v>AVerdugo</v>
+        <v>ACARTERA1</v>
       </c>
       <c r="Y222" t="str">
-        <v>AVerdugo</v>
+        <v>ACARTERA1</v>
       </c>
       <c r="Z222" t="str">
         <v>SIN DATOS</v>
       </c>
+      <c r="AA222" t="str">
+        <v>SIKIU AVENDAÑO</v>
+      </c>
       <c r="AB222" t="str">
-        <v>CajaParque</v>
+        <v>CajaLider</v>
       </c>
       <c r="AC222" t="str">
         <v>SIN DATOS</v>
@@ -28303,10 +28267,10 @@
         <v>AL DIA</v>
       </c>
       <c r="AE222">
-        <v>-360</v>
+        <v>-176</v>
       </c>
       <c r="AF222">
-        <v>361</v>
+        <v>3</v>
       </c>
       <c r="AG222">
         <v>0</v>
@@ -28321,22 +28285,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK222">
-        <v>220938</v>
+        <v>220899</v>
       </c>
       <c r="AM222">
-        <v>13760</v>
+        <v>10724</v>
       </c>
       <c r="AQ222" t="str">
-        <v>MANT 2 UF NF - PROP: 1013130 - 1-AF-17</v>
+        <v>MANTENIMIENTO 2.000 UF</v>
       </c>
       <c r="AR222" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS222" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT222" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU222" t="str">
         <v>SEPULTURA</v>
@@ -28347,19 +28308,16 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B223" t="str">
-        <v>7084246-7</v>
+        <v>10840340-3</v>
       </c>
       <c r="C223" t="str">
-        <v>CORTES PAUZOCA PAUZOCA JOSE ANTONIO</v>
+        <v>PARRA LEFIÑANCO MARIA MERCEDES</v>
       </c>
       <c r="D223" t="str">
         <v>SANTIAGO</v>
       </c>
-      <c r="F223" t="str">
-        <v>VALLES UNIDOS CENTRO</v>
-      </c>
       <c r="G223">
-        <v>737</v>
+        <v>1013130</v>
       </c>
       <c r="H223" t="str">
         <v>ACTIVO VALIDADO</v>
@@ -28371,19 +28329,19 @@
         <v>2.38</v>
       </c>
       <c r="K223">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L223">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M223" t="str">
         <v>04/10/2026</v>
       </c>
       <c r="N223">
-        <v>2.38</v>
+        <v>1.153</v>
       </c>
       <c r="O223">
-        <v>97794</v>
+        <v>47377</v>
       </c>
       <c r="P223" t="str">
         <v>SIN DATOS</v>
@@ -28392,16 +28350,13 @@
         <v>4</v>
       </c>
       <c r="R223">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="S223">
         <v>41089.96</v>
       </c>
       <c r="T223">
-        <v>11</v>
-      </c>
-      <c r="U223" t="str">
-        <v>OFICINA</v>
+        <v>7</v>
       </c>
       <c r="V223" t="str">
         <v>Tarjetas de Debito</v>
@@ -28418,9 +28373,6 @@
       <c r="Z223" t="str">
         <v>SIN DATOS</v>
       </c>
-      <c r="AA223" t="str">
-        <v>SIKIU AVENDAÑO</v>
-      </c>
       <c r="AB223" t="str">
         <v>CajaParque</v>
       </c>
@@ -28428,13 +28380,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD223" t="str">
-        <v>MAS DE 120 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE223">
-        <v>-177</v>
+        <v>-359</v>
       </c>
       <c r="AF223">
-        <v>1</v>
+        <v>362</v>
       </c>
       <c r="AG223">
         <v>0</v>
@@ -28449,22 +28401,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK223">
-        <v>220950</v>
+        <v>220938</v>
       </c>
       <c r="AM223">
-        <v>10737</v>
+        <v>13760</v>
       </c>
       <c r="AQ223" t="str">
-        <v>MANTENIMIENTO 2.000 UF</v>
+        <v>MANT 2 UF NF - PROP: 1013130 - 1-AF-17</v>
       </c>
       <c r="AR223" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS223" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT223" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU223" t="str">
         <v>SEPULTURA</v>
@@ -28475,19 +28424,16 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B224" t="str">
-        <v>7084246-7</v>
+        <v>10840340-3</v>
       </c>
       <c r="C224" t="str">
-        <v>CORTES PAUZOCA PAUZOCA JOSE ANTONIO</v>
+        <v>PARRA LEFIÑANCO MARIA MERCEDES</v>
       </c>
       <c r="D224" t="str">
         <v>SANTIAGO</v>
       </c>
-      <c r="F224" t="str">
-        <v>VALLES UNIDOS CENTRO</v>
-      </c>
       <c r="G224">
-        <v>737</v>
+        <v>1013130</v>
       </c>
       <c r="H224" t="str">
         <v>ACTIVO VALIDADO</v>
@@ -28499,19 +28445,19 @@
         <v>2.38</v>
       </c>
       <c r="K224">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L224">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M224" t="str">
         <v>04/10/2026</v>
       </c>
       <c r="N224">
-        <v>2.38</v>
+        <v>1.153</v>
       </c>
       <c r="O224">
-        <v>97794</v>
+        <v>47377</v>
       </c>
       <c r="P224" t="str">
         <v>SIN DATOS</v>
@@ -28520,16 +28466,13 @@
         <v>4</v>
       </c>
       <c r="R224">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="S224">
         <v>41089.96</v>
       </c>
       <c r="T224">
-        <v>12</v>
-      </c>
-      <c r="U224" t="str">
-        <v>OFICINA</v>
+        <v>7</v>
       </c>
       <c r="V224" t="str">
         <v>Tarjetas de Debito</v>
@@ -28546,9 +28489,6 @@
       <c r="Z224" t="str">
         <v>SIN DATOS</v>
       </c>
-      <c r="AA224" t="str">
-        <v>SIKIU AVENDAÑO</v>
-      </c>
       <c r="AB224" t="str">
         <v>CajaParque</v>
       </c>
@@ -28556,13 +28496,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD224" t="str">
-        <v>MAS DE 120 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE224">
-        <v>-177</v>
+        <v>-359</v>
       </c>
       <c r="AF224">
-        <v>1</v>
+        <v>362</v>
       </c>
       <c r="AG224">
         <v>0</v>
@@ -28577,22 +28517,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK224">
-        <v>220950</v>
+        <v>220938</v>
       </c>
       <c r="AM224">
-        <v>10737</v>
+        <v>13760</v>
       </c>
       <c r="AQ224" t="str">
-        <v>MANTENIMIENTO 2.000 UF</v>
+        <v>MANT 2 UF NF - PROP: 1013130 - 1-AF-17</v>
       </c>
       <c r="AR224" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS224" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT224" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU224" t="str">
         <v>SEPULTURA</v>
@@ -28654,7 +28591,7 @@
         <v>41089.96</v>
       </c>
       <c r="T225">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U225" t="str">
         <v>OFICINA</v>
@@ -28687,10 +28624,10 @@
         <v>MAS DE 120 D</v>
       </c>
       <c r="AE225">
-        <v>-177</v>
+        <v>-176</v>
       </c>
       <c r="AF225">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG225">
         <v>0</v>
@@ -28714,13 +28651,10 @@
         <v>MANTENIMIENTO 2.000 UF</v>
       </c>
       <c r="AR225" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS225" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT225" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU225" t="str">
         <v>SEPULTURA</v>
@@ -28731,40 +28665,43 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B226" t="str">
-        <v>13036214-1</v>
+        <v>7084246-7</v>
       </c>
       <c r="C226" t="str">
-        <v>FERNANDEZ PEREZ ALEJANDRA INES</v>
+        <v>CORTES PAUZOCA PAUZOCA JOSE ANTONIO</v>
       </c>
       <c r="D226" t="str">
         <v>SANTIAGO</v>
       </c>
+      <c r="F226" t="str">
+        <v>VALLES UNIDOS CENTRO</v>
+      </c>
       <c r="G226">
-        <v>1014096</v>
+        <v>737</v>
       </c>
       <c r="H226" t="str">
         <v>ACTIVO VALIDADO</v>
       </c>
       <c r="I226">
-        <v>97814</v>
+        <v>97794</v>
       </c>
       <c r="J226">
         <v>2.38</v>
       </c>
       <c r="K226">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L226">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M226" t="str">
-        <v>05/10/2026</v>
+        <v>04/10/2026</v>
       </c>
       <c r="N226">
         <v>2.38</v>
       </c>
       <c r="O226">
-        <v>97814</v>
+        <v>97794</v>
       </c>
       <c r="P226" t="str">
         <v>SIN DATOS</v>
@@ -28773,13 +28710,13 @@
         <v>4</v>
       </c>
       <c r="R226">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="S226">
-        <v>41098.15</v>
+        <v>41089.96</v>
       </c>
       <c r="T226">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="U226" t="str">
         <v>OFICINA</v>
@@ -28799,6 +28736,9 @@
       <c r="Z226" t="str">
         <v>SIN DATOS</v>
       </c>
+      <c r="AA226" t="str">
+        <v>SIKIU AVENDAÑO</v>
+      </c>
       <c r="AB226" t="str">
         <v>CajaParque</v>
       </c>
@@ -28806,13 +28746,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD226" t="str">
-        <v>HASTA 60 D</v>
+        <v>MAS DE 120 D</v>
       </c>
       <c r="AE226">
-        <v>-268</v>
+        <v>-176</v>
       </c>
       <c r="AF226">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG226">
         <v>0</v>
@@ -28827,22 +28767,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK226">
-        <v>220966</v>
+        <v>220950</v>
       </c>
       <c r="AM226">
-        <v>15759</v>
+        <v>10737</v>
       </c>
       <c r="AQ226" t="str">
-        <v>MANT 2 UF NI - PROP: 1014096 - 1-BE-15</v>
+        <v>MANTENIMIENTO 2.000 UF</v>
       </c>
       <c r="AR226" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS226" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT226" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU226" t="str">
         <v>SEPULTURA</v>
@@ -28853,40 +28790,43 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B227" t="str">
-        <v>10714431-5</v>
+        <v>7084246-7</v>
       </c>
       <c r="C227" t="str">
-        <v>ESPINOSA ARAVENA ARAVENA ADRIANA DE FATIMA</v>
+        <v>CORTES PAUZOCA PAUZOCA JOSE ANTONIO</v>
       </c>
       <c r="D227" t="str">
         <v>SANTIAGO</v>
       </c>
+      <c r="F227" t="str">
+        <v>VALLES UNIDOS CENTRO</v>
+      </c>
       <c r="G227">
-        <v>235</v>
+        <v>737</v>
       </c>
       <c r="H227" t="str">
         <v>ACTIVO VALIDADO</v>
       </c>
       <c r="I227">
-        <v>97814</v>
+        <v>97794</v>
       </c>
       <c r="J227">
         <v>2.38</v>
       </c>
       <c r="K227">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L227">
         <v>31</v>
       </c>
       <c r="M227" t="str">
-        <v>05/10/2026</v>
+        <v>04/10/2026</v>
       </c>
       <c r="N227">
         <v>2.38</v>
       </c>
       <c r="O227">
-        <v>97814</v>
+        <v>97794</v>
       </c>
       <c r="P227" t="str">
         <v>SIN DATOS</v>
@@ -28895,13 +28835,16 @@
         <v>4</v>
       </c>
       <c r="R227">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S227">
-        <v>41098.15</v>
+        <v>41089.96</v>
       </c>
       <c r="T227">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="U227" t="str">
+        <v>OFICINA</v>
       </c>
       <c r="V227" t="str">
         <v>Tarjetas de Debito</v>
@@ -28910,28 +28853,31 @@
         <v>UF</v>
       </c>
       <c r="X227" t="str">
-        <v>ACARTERA1</v>
+        <v>AVerdugo</v>
       </c>
       <c r="Y227" t="str">
-        <v>ACARTERA1</v>
+        <v>AVerdugo</v>
       </c>
       <c r="Z227" t="str">
         <v>SIN DATOS</v>
       </c>
+      <c r="AA227" t="str">
+        <v>SIKIU AVENDAÑO</v>
+      </c>
       <c r="AB227" t="str">
-        <v>CajaLider</v>
+        <v>CajaParque</v>
       </c>
       <c r="AC227" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="AD227" t="str">
-        <v>AL DIA</v>
+        <v>MAS DE 120 D</v>
       </c>
       <c r="AE227">
-        <v>-299</v>
+        <v>-176</v>
       </c>
       <c r="AF227">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG227">
         <v>0</v>
@@ -28946,22 +28892,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK227">
-        <v>220968</v>
+        <v>220950</v>
       </c>
       <c r="AM227">
-        <v>111</v>
+        <v>10737</v>
       </c>
       <c r="AQ227" t="str">
-        <v>CATEGORIA 2 UF - PROP: 235 - 3232.000000000000</v>
+        <v>MANTENIMIENTO 2.000 UF</v>
       </c>
       <c r="AR227" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS227" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT227" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU227" t="str">
         <v>SEPULTURA</v>
@@ -28972,88 +28915,88 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B228" t="str">
-        <v>6792656-0</v>
+        <v>13036214-1</v>
       </c>
       <c r="C228" t="str">
-        <v>ARCE AYALA PEDRO ARMANDO</v>
+        <v>FERNANDEZ PEREZ ALEJANDRA INES</v>
       </c>
       <c r="D228" t="str">
         <v>SANTIAGO</v>
       </c>
       <c r="G228">
-        <v>1013506</v>
+        <v>1014096</v>
       </c>
       <c r="H228" t="str">
         <v>ACTIVO VALIDADO</v>
       </c>
       <c r="I228">
-        <v>97755</v>
+        <v>97814</v>
       </c>
       <c r="J228">
         <v>2.38</v>
       </c>
       <c r="K228">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L228">
         <v>30</v>
       </c>
       <c r="M228" t="str">
-        <v>02/10/2026</v>
+        <v>05/10/2026</v>
       </c>
       <c r="N228">
-        <v>1.255</v>
+        <v>2.38</v>
       </c>
       <c r="O228">
-        <v>51547</v>
+        <v>97814</v>
       </c>
       <c r="P228" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="Q228">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R228">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S228">
-        <v>41073.57</v>
+        <v>41098.15</v>
       </c>
       <c r="T228">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="U228" t="str">
+        <v>OFICINA</v>
       </c>
       <c r="V228" t="str">
-        <v>BANCO ESTADO</v>
+        <v>Tarjetas de Debito</v>
       </c>
       <c r="W228" t="str">
         <v>UF</v>
       </c>
       <c r="X228" t="str">
-        <v>ACARTERA1</v>
+        <v>AVerdugo</v>
       </c>
       <c r="Y228" t="str">
-        <v>ACARTERA1</v>
+        <v>AVerdugo</v>
       </c>
       <c r="Z228" t="str">
         <v>SIN DATOS</v>
       </c>
-      <c r="AA228" t="str">
-        <v>ALBANY JASPE</v>
-      </c>
       <c r="AB228" t="str">
-        <v>CajaLider</v>
+        <v>CajaParque</v>
       </c>
       <c r="AC228" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="AD228" t="str">
-        <v>MAS DE 120 D</v>
+        <v>HASTA 60 D</v>
       </c>
       <c r="AE228">
-        <v>5</v>
+        <v>-267</v>
       </c>
       <c r="AF228">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG228">
         <v>0</v>
@@ -29068,22 +29011,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK228">
-        <v>220982</v>
+        <v>220966</v>
       </c>
       <c r="AM228">
-        <v>14552</v>
+        <v>15759</v>
       </c>
       <c r="AQ228" t="str">
-        <v>MANT 2 UF NF - PROP: 1013506 - 4-C-28</v>
+        <v>MANT 2 UF NI - PROP: 1014096 - 1-BE-15</v>
       </c>
       <c r="AR228" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS228" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT228" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU228" t="str">
         <v>SEPULTURA</v>
@@ -29094,58 +29034,58 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B229" t="str">
-        <v>6792656-0</v>
+        <v>10714431-5</v>
       </c>
       <c r="C229" t="str">
-        <v>ARCE AYALA PEDRO ARMANDO</v>
+        <v>ESPINOSA ARAVENA ARAVENA ADRIANA DE FATIMA</v>
       </c>
       <c r="D229" t="str">
         <v>SANTIAGO</v>
       </c>
       <c r="G229">
-        <v>1013506</v>
+        <v>235</v>
       </c>
       <c r="H229" t="str">
         <v>ACTIVO VALIDADO</v>
       </c>
       <c r="I229">
-        <v>97755</v>
+        <v>97814</v>
       </c>
       <c r="J229">
         <v>2.38</v>
       </c>
       <c r="K229">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L229">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M229" t="str">
-        <v>02/10/2026</v>
+        <v>05/10/2026</v>
       </c>
       <c r="N229">
-        <v>1.13</v>
+        <v>2.38</v>
       </c>
       <c r="O229">
-        <v>46413</v>
+        <v>97814</v>
       </c>
       <c r="P229" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="Q229">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R229">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="S229">
-        <v>41073.57</v>
+        <v>41098.15</v>
       </c>
       <c r="T229">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="V229" t="str">
-        <v>BANCO ESTADO</v>
+        <v>Tarjetas de Debito</v>
       </c>
       <c r="W229" t="str">
         <v>UF</v>
@@ -29159,9 +29099,6 @@
       <c r="Z229" t="str">
         <v>SIN DATOS</v>
       </c>
-      <c r="AA229" t="str">
-        <v>ALBANY JASPE</v>
-      </c>
       <c r="AB229" t="str">
         <v>CajaLider</v>
       </c>
@@ -29169,13 +29106,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD229" t="str">
-        <v>MAS DE 120 D</v>
+        <v>AL DIA</v>
       </c>
       <c r="AE229">
-        <v>5</v>
+        <v>-298</v>
       </c>
       <c r="AF229">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG229">
         <v>0</v>
@@ -29190,22 +29127,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK229">
-        <v>220982</v>
+        <v>220968</v>
       </c>
       <c r="AM229">
-        <v>14552</v>
+        <v>111</v>
       </c>
       <c r="AQ229" t="str">
-        <v>MANT 2 UF NF - PROP: 1013506 - 4-C-28</v>
+        <v>CATEGORIA 2 UF - PROP: 235 - 3232.000000000000</v>
       </c>
       <c r="AR229" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS229" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT229" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU229" t="str">
         <v>SEPULTURA</v>
@@ -29216,31 +29150,28 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B230" t="str">
-        <v>7393525-3</v>
+        <v>6792656-0</v>
       </c>
       <c r="C230" t="str">
-        <v>VALENZUELA VALENZUEL JOSE RUBEN</v>
+        <v>ARCE AYALA PEDRO ARMANDO</v>
       </c>
       <c r="D230" t="str">
-        <v>Metropolitana</v>
-      </c>
-      <c r="E230" t="str">
-        <v>Lampa</v>
+        <v>SANTIAGO</v>
       </c>
       <c r="G230">
-        <v>1013862</v>
+        <v>1013506</v>
       </c>
       <c r="H230" t="str">
         <v>ACTIVO VALIDADO</v>
       </c>
       <c r="I230">
-        <v>82147</v>
+        <v>97755</v>
       </c>
       <c r="J230">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="K230">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L230">
         <v>30</v>
@@ -29249,28 +29180,25 @@
         <v>02/10/2026</v>
       </c>
       <c r="N230">
-        <v>1.217</v>
+        <v>1.255</v>
       </c>
       <c r="O230">
-        <v>49987</v>
+        <v>51547</v>
       </c>
       <c r="P230" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="Q230">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R230">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S230">
         <v>41073.57</v>
       </c>
       <c r="T230">
-        <v>1</v>
-      </c>
-      <c r="U230" t="str">
-        <v>OFICINA</v>
+        <v>5</v>
       </c>
       <c r="V230" t="str">
         <v>BANCO ESTADO</v>
@@ -29300,10 +29228,10 @@
         <v>MAS DE 120 D</v>
       </c>
       <c r="AE230">
-        <v>888</v>
+        <v>6</v>
       </c>
       <c r="AF230">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG230">
         <v>0</v>
@@ -29318,22 +29246,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK230">
-        <v>220995</v>
+        <v>220982</v>
       </c>
       <c r="AM230">
-        <v>15284</v>
+        <v>14552</v>
       </c>
       <c r="AQ230" t="str">
-        <v>MANT 2 UF NF - PROP: 1013862 - 4-I-31</v>
+        <v>MANT 2 UF NF - PROP: 1013506 - 4-C-28</v>
       </c>
       <c r="AR230" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS230" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT230" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU230" t="str">
         <v>SEPULTURA</v>
@@ -29344,16 +29269,16 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B231" t="str">
-        <v>13676688-0</v>
+        <v>6792656-0</v>
       </c>
       <c r="C231" t="str">
-        <v>SEPULVEDA RIVERA RIVERA MABEL NAYADEE</v>
+        <v>ARCE AYALA PEDRO ARMANDO</v>
       </c>
       <c r="D231" t="str">
         <v>SANTIAGO</v>
       </c>
       <c r="G231">
-        <v>1013091</v>
+        <v>1013506</v>
       </c>
       <c r="H231" t="str">
         <v>ACTIVO VALIDADO</v>
@@ -29365,34 +29290,34 @@
         <v>2.38</v>
       </c>
       <c r="K231">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L231">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M231" t="str">
         <v>02/10/2026</v>
       </c>
       <c r="N231">
-        <v>2.38</v>
+        <v>1.13</v>
       </c>
       <c r="O231">
-        <v>97755</v>
+        <v>46413</v>
       </c>
       <c r="P231" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="Q231">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R231">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S231">
         <v>41073.57</v>
       </c>
       <c r="T231">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V231" t="str">
         <v>BANCO ESTADO</v>
@@ -29410,7 +29335,7 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AA231" t="str">
-        <v>SIKIU AVENDAÑO</v>
+        <v>ALBANY JASPE</v>
       </c>
       <c r="AB231" t="str">
         <v>CajaLider</v>
@@ -29419,13 +29344,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD231" t="str">
-        <v>HASTA 30 D</v>
+        <v>MAS DE 120 D</v>
       </c>
       <c r="AE231">
-        <v>-299</v>
+        <v>6</v>
       </c>
       <c r="AF231">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG231">
         <v>0</v>
@@ -29440,22 +29365,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK231">
-        <v>220997</v>
+        <v>220982</v>
       </c>
       <c r="AM231">
-        <v>13668</v>
+        <v>14552</v>
       </c>
       <c r="AQ231" t="str">
-        <v>MANT 2 UF NF - PROP: 1013091 - 3-BE-38</v>
+        <v>MANT 2 UF NF - PROP: 1013506 - 4-C-28</v>
       </c>
       <c r="AR231" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS231" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT231" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU231" t="str">
         <v>SEPULTURA</v>
@@ -29466,55 +29388,61 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B232" t="str">
-        <v>13676688-0</v>
+        <v>7393525-3</v>
       </c>
       <c r="C232" t="str">
-        <v>SEPULVEDA RIVERA RIVERA MABEL NAYADEE</v>
+        <v>VALENZUELA VALENZUELA JOSE RUBEN</v>
       </c>
       <c r="D232" t="str">
-        <v>SANTIAGO</v>
+        <v>Metropolitana</v>
+      </c>
+      <c r="E232" t="str">
+        <v>Lampa</v>
       </c>
       <c r="G232">
-        <v>1013091</v>
+        <v>1013862</v>
       </c>
       <c r="H232" t="str">
         <v>ACTIVO VALIDADO</v>
       </c>
       <c r="I232">
-        <v>97755</v>
+        <v>82147</v>
       </c>
       <c r="J232">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="K232">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L232">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M232" t="str">
         <v>02/10/2026</v>
       </c>
       <c r="N232">
-        <v>2.38</v>
+        <v>1.217</v>
       </c>
       <c r="O232">
-        <v>97755</v>
+        <v>49987</v>
       </c>
       <c r="P232" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="Q232">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R232">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S232">
         <v>41073.57</v>
       </c>
       <c r="T232">
-        <v>7</v>
+        <v>1</v>
+      </c>
+      <c r="U232" t="str">
+        <v>OFICINA</v>
       </c>
       <c r="V232" t="str">
         <v>BANCO ESTADO</v>
@@ -29532,7 +29460,7 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AA232" t="str">
-        <v>SIKIU AVENDAÑO</v>
+        <v>ALBANY JASPE</v>
       </c>
       <c r="AB232" t="str">
         <v>CajaLider</v>
@@ -29541,13 +29469,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD232" t="str">
-        <v>HASTA 30 D</v>
+        <v>MAS DE 120 D</v>
       </c>
       <c r="AE232">
-        <v>-299</v>
+        <v>889</v>
       </c>
       <c r="AF232">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG232">
         <v>0</v>
@@ -29562,22 +29490,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK232">
-        <v>220997</v>
+        <v>220995</v>
       </c>
       <c r="AM232">
-        <v>13668</v>
+        <v>15284</v>
       </c>
       <c r="AQ232" t="str">
-        <v>MANT 2 UF NF - PROP: 1013091 - 3-BE-38</v>
+        <v>MANT 2 UF NF - PROP: 1013862 - 4-I-31</v>
       </c>
       <c r="AR232" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS232" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT232" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU232" t="str">
         <v>SEPULTURA</v>
@@ -29588,16 +29513,16 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B233" t="str">
-        <v>8765418-4</v>
+        <v>13676688-0</v>
       </c>
       <c r="C233" t="str">
-        <v>AGUILERA PLAZA GLADYS CECILIA</v>
+        <v>SEPULVEDA RIVERA RIVERA MABEL NAYADEE</v>
       </c>
       <c r="D233" t="str">
         <v>SANTIAGO</v>
       </c>
       <c r="G233">
-        <v>101008</v>
+        <v>1013091</v>
       </c>
       <c r="H233" t="str">
         <v>ACTIVO VALIDADO</v>
@@ -29609,10 +29534,10 @@
         <v>2.38</v>
       </c>
       <c r="K233">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L233">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M233" t="str">
         <v>02/10/2026</v>
@@ -29627,16 +29552,16 @@
         <v>SIN DATOS</v>
       </c>
       <c r="Q233">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R233">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S233">
         <v>41073.57</v>
       </c>
       <c r="T233">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V233" t="str">
         <v>BANCO ESTADO</v>
@@ -29653,6 +29578,9 @@
       <c r="Z233" t="str">
         <v>SIN DATOS</v>
       </c>
+      <c r="AA233" t="str">
+        <v>SIKIU AVENDAÑO</v>
+      </c>
       <c r="AB233" t="str">
         <v>CajaLider</v>
       </c>
@@ -29660,13 +29588,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD233" t="str">
-        <v>MAS DE 120 D</v>
+        <v>HASTA 30 D</v>
       </c>
       <c r="AE233">
-        <v>370</v>
+        <v>-298</v>
       </c>
       <c r="AF233">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG233">
         <v>0</v>
@@ -29681,22 +29609,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK233">
-        <v>221009</v>
+        <v>220997</v>
       </c>
       <c r="AM233">
-        <v>485</v>
+        <v>13668</v>
       </c>
       <c r="AQ233" t="str">
-        <v>MANT 2 UF NF - PROP: 101008 - 5-E-78</v>
+        <v>MANT 2 UF NF - PROP: 1013091 - 3-BE-38</v>
       </c>
       <c r="AR233" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS233" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT233" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU233" t="str">
         <v>SEPULTURA</v>
@@ -29707,16 +29632,16 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B234" t="str">
-        <v>8765418-4</v>
+        <v>13676688-0</v>
       </c>
       <c r="C234" t="str">
-        <v>AGUILERA PLAZA GLADYS CECILIA</v>
+        <v>SEPULVEDA RIVERA RIVERA MABEL NAYADEE</v>
       </c>
       <c r="D234" t="str">
         <v>SANTIAGO</v>
       </c>
       <c r="G234">
-        <v>101008</v>
+        <v>1013091</v>
       </c>
       <c r="H234" t="str">
         <v>ACTIVO VALIDADO</v>
@@ -29728,34 +29653,34 @@
         <v>2.38</v>
       </c>
       <c r="K234">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L234">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M234" t="str">
         <v>02/10/2026</v>
       </c>
       <c r="N234">
-        <v>0.242</v>
+        <v>2.38</v>
       </c>
       <c r="O234">
-        <v>9940</v>
+        <v>97755</v>
       </c>
       <c r="P234" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="Q234">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R234">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S234">
         <v>41073.57</v>
       </c>
       <c r="T234">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V234" t="str">
         <v>BANCO ESTADO</v>
@@ -29772,6 +29697,9 @@
       <c r="Z234" t="str">
         <v>SIN DATOS</v>
       </c>
+      <c r="AA234" t="str">
+        <v>SIKIU AVENDAÑO</v>
+      </c>
       <c r="AB234" t="str">
         <v>CajaLider</v>
       </c>
@@ -29779,13 +29707,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD234" t="str">
-        <v>MAS DE 120 D</v>
+        <v>HASTA 30 D</v>
       </c>
       <c r="AE234">
-        <v>370</v>
+        <v>-298</v>
       </c>
       <c r="AF234">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG234">
         <v>0</v>
@@ -29800,22 +29728,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK234">
-        <v>221009</v>
+        <v>220997</v>
       </c>
       <c r="AM234">
-        <v>485</v>
+        <v>13668</v>
       </c>
       <c r="AQ234" t="str">
-        <v>MANT 2 UF NF - PROP: 101008 - 5-E-78</v>
+        <v>MANT 2 UF NF - PROP: 1013091 - 3-BE-38</v>
       </c>
       <c r="AR234" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS234" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT234" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU234" t="str">
         <v>SEPULTURA</v>
@@ -29856,10 +29781,10 @@
         <v>02/10/2026</v>
       </c>
       <c r="N235">
-        <v>2.247</v>
+        <v>2.38</v>
       </c>
       <c r="O235">
-        <v>92292</v>
+        <v>97755</v>
       </c>
       <c r="P235" t="str">
         <v>SIN DATOS</v>
@@ -29874,7 +29799,7 @@
         <v>41073.57</v>
       </c>
       <c r="T235">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V235" t="str">
         <v>BANCO ESTADO</v>
@@ -29901,10 +29826,10 @@
         <v>MAS DE 120 D</v>
       </c>
       <c r="AE235">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AF235">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG235">
         <v>0</v>
@@ -29928,13 +29853,10 @@
         <v>MANT 2 UF NF - PROP: 101008 - 5-E-78</v>
       </c>
       <c r="AR235" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS235" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT235" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU235" t="str">
         <v>SEPULTURA</v>
@@ -29945,40 +29867,40 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B236" t="str">
-        <v>6558834-K</v>
+        <v>8765418-4</v>
       </c>
       <c r="C236" t="str">
-        <v>PEÑA ROJAS ISABEL BERNARDA</v>
+        <v>AGUILERA PLAZA GLADYS CECILIA</v>
       </c>
       <c r="D236" t="str">
         <v>SANTIAGO</v>
       </c>
       <c r="G236">
-        <v>1013045</v>
+        <v>101008</v>
       </c>
       <c r="H236" t="str">
         <v>ACTIVO VALIDADO</v>
       </c>
       <c r="I236">
-        <v>97814</v>
+        <v>97755</v>
       </c>
       <c r="J236">
         <v>2.38</v>
       </c>
       <c r="K236">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L236">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M236" t="str">
-        <v>05/10/2026</v>
+        <v>02/10/2026</v>
       </c>
       <c r="N236">
-        <v>0.487</v>
+        <v>0.242</v>
       </c>
       <c r="O236">
-        <v>20015</v>
+        <v>9940</v>
       </c>
       <c r="P236" t="str">
         <v>SIN DATOS</v>
@@ -29987,16 +29909,16 @@
         <v>6</v>
       </c>
       <c r="R236">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S236">
-        <v>41098.15</v>
+        <v>41073.57</v>
       </c>
       <c r="T236">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V236" t="str">
-        <v>EFECTIVO</v>
+        <v>BANCO ESTADO</v>
       </c>
       <c r="W236" t="str">
         <v>UF</v>
@@ -30010,9 +29932,6 @@
       <c r="Z236" t="str">
         <v>SIN DATOS</v>
       </c>
-      <c r="AA236" t="str">
-        <v>SIKIU AVENDAÑO</v>
-      </c>
       <c r="AB236" t="str">
         <v>CajaLider</v>
       </c>
@@ -30020,13 +29939,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD236" t="str">
-        <v>HASTA 90 D</v>
+        <v>MAS DE 120 D</v>
       </c>
       <c r="AE236">
-        <v>492</v>
+        <v>371</v>
       </c>
       <c r="AF236">
-        <v>334</v>
+        <v>4</v>
       </c>
       <c r="AG236">
         <v>0</v>
@@ -30041,22 +29960,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK236">
-        <v>221080</v>
+        <v>221009</v>
       </c>
       <c r="AM236">
-        <v>13569</v>
+        <v>485</v>
       </c>
       <c r="AQ236" t="str">
-        <v>MANT 2 UF NF - PROP: 1013045 - 3-AE-24</v>
+        <v>MANT 2 UF NF - PROP: 101008 - 5-E-78</v>
       </c>
       <c r="AR236" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS236" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT236" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU236" t="str">
         <v>SEPULTURA</v>
@@ -30067,58 +29983,58 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B237" t="str">
-        <v>10781693-3</v>
+        <v>8765418-4</v>
       </c>
       <c r="C237" t="str">
-        <v>SANCHEZ MELLADO MELLADO JUAN HERNAN</v>
+        <v>AGUILERA PLAZA GLADYS CECILIA</v>
       </c>
       <c r="D237" t="str">
         <v>SANTIAGO</v>
       </c>
       <c r="G237">
-        <v>313</v>
+        <v>101008</v>
       </c>
       <c r="H237" t="str">
         <v>ACTIVO VALIDADO</v>
       </c>
       <c r="I237">
-        <v>97814</v>
+        <v>97755</v>
       </c>
       <c r="J237">
         <v>2.38</v>
       </c>
       <c r="K237">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="L237">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M237" t="str">
-        <v>05/10/2026</v>
+        <v>02/10/2026</v>
       </c>
       <c r="N237">
-        <v>2.38</v>
+        <v>2.247</v>
       </c>
       <c r="O237">
-        <v>97814</v>
+        <v>92292</v>
       </c>
       <c r="P237" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="Q237">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R237">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="S237">
-        <v>41098.15</v>
+        <v>41073.57</v>
       </c>
       <c r="T237">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="V237" t="str">
-        <v>EFECTIVO</v>
+        <v>BANCO ESTADO</v>
       </c>
       <c r="W237" t="str">
         <v>UF</v>
@@ -30139,13 +30055,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD237" t="str">
-        <v>HASTA 30 D</v>
+        <v>MAS DE 120 D</v>
       </c>
       <c r="AE237">
-        <v>-299</v>
+        <v>371</v>
       </c>
       <c r="AF237">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG237">
         <v>0</v>
@@ -30160,22 +30076,19 @@
         <v>Cobro</v>
       </c>
       <c r="AK237">
-        <v>221086</v>
+        <v>221009</v>
       </c>
       <c r="AM237">
-        <v>80</v>
+        <v>485</v>
       </c>
       <c r="AQ237" t="str">
-        <v>CATEGORIA 2 UF - PROP: 313 - 3910.000000000000</v>
+        <v>MANT 2 UF NF - PROP: 101008 - 5-E-78</v>
       </c>
       <c r="AR237" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS237" t="str">
-        <v/>
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
       </c>
       <c r="AT237" t="str">
-        <v>945718455</v>
+        <v>56999664236</v>
       </c>
       <c r="AU237" t="str">
         <v>SEPULTURA</v>
@@ -30186,22 +30099,16 @@
         <v>VALLES UNIDOS S.A.</v>
       </c>
       <c r="B238" t="str">
-        <v>210394818</v>
+        <v>6558834-K</v>
       </c>
       <c r="C238" t="str">
-        <v>BRICEÑO VENEGAS BASTIAN FELIPE</v>
+        <v>PEÑA ROJAS ISABEL BERNARDA</v>
       </c>
       <c r="D238" t="str">
-        <v>Metropolitana</v>
-      </c>
-      <c r="E238" t="str">
-        <v>Quilicura</v>
-      </c>
-      <c r="F238" t="str">
-        <v>VALLES UNIDOS CENTRO</v>
+        <v>SANTIAGO</v>
       </c>
       <c r="G238">
-        <v>1014772</v>
+        <v>1013045</v>
       </c>
       <c r="H238" t="str">
         <v>ACTIVO VALIDADO</v>
@@ -30213,7 +30120,7 @@
         <v>2.38</v>
       </c>
       <c r="K238">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L238">
         <v>31</v>
@@ -30222,31 +30129,28 @@
         <v>05/10/2026</v>
       </c>
       <c r="N238">
-        <v>2.38</v>
+        <v>0.487</v>
       </c>
       <c r="O238">
-        <v>97814</v>
+        <v>20015</v>
       </c>
       <c r="P238" t="str">
         <v>SIN DATOS</v>
       </c>
       <c r="Q238">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R238">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S238">
         <v>41098.15</v>
       </c>
       <c r="T238">
-        <v>1</v>
-      </c>
-      <c r="U238" t="str">
-        <v>OFICINA</v>
+        <v>6</v>
       </c>
       <c r="V238" t="str">
-        <v>BANCO ESTADO</v>
+        <v>EFECTIVO</v>
       </c>
       <c r="W238" t="str">
         <v>UF</v>
@@ -30260,6 +30164,9 @@
       <c r="Z238" t="str">
         <v>SIN DATOS</v>
       </c>
+      <c r="AA238" t="str">
+        <v>SIKIU AVENDAÑO</v>
+      </c>
       <c r="AB238" t="str">
         <v>CajaLider</v>
       </c>
@@ -30267,13 +30174,13 @@
         <v>SIN DATOS</v>
       </c>
       <c r="AD238" t="str">
-        <v>AL DIA</v>
+        <v>HASTA 90 D</v>
       </c>
       <c r="AE238">
-        <v>-391</v>
+        <v>493</v>
       </c>
       <c r="AF238">
-        <v>0</v>
+        <v>335</v>
       </c>
       <c r="AG238">
         <v>0</v>
@@ -30288,30 +30195,268 @@
         <v>Cobro</v>
       </c>
       <c r="AK238">
+        <v>221080</v>
+      </c>
+      <c r="AM238">
+        <v>13569</v>
+      </c>
+      <c r="AQ238" t="str">
+        <v>MANT 2 UF NF - PROP: 1013045 - 3-AE-24</v>
+      </c>
+      <c r="AR238" t="str">
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
+      </c>
+      <c r="AT238" t="str">
+        <v>56999664236</v>
+      </c>
+      <c r="AU238" t="str">
+        <v>SEPULTURA</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>VALLES UNIDOS S.A.</v>
+      </c>
+      <c r="B239" t="str">
+        <v>10781693-3</v>
+      </c>
+      <c r="C239" t="str">
+        <v>SANCHEZ MELLADO MELLADO JUAN HERNAN</v>
+      </c>
+      <c r="D239" t="str">
+        <v>SANTIAGO</v>
+      </c>
+      <c r="G239">
+        <v>313</v>
+      </c>
+      <c r="H239" t="str">
+        <v>ACTIVO VALIDADO</v>
+      </c>
+      <c r="I239">
+        <v>97814</v>
+      </c>
+      <c r="J239">
+        <v>2.38</v>
+      </c>
+      <c r="K239">
+        <v>18</v>
+      </c>
+      <c r="L239">
+        <v>31</v>
+      </c>
+      <c r="M239" t="str">
+        <v>05/10/2026</v>
+      </c>
+      <c r="N239">
+        <v>2.38</v>
+      </c>
+      <c r="O239">
+        <v>97814</v>
+      </c>
+      <c r="P239" t="str">
+        <v>SIN DATOS</v>
+      </c>
+      <c r="Q239">
+        <v>4</v>
+      </c>
+      <c r="R239">
+        <v>14</v>
+      </c>
+      <c r="S239">
+        <v>41098.15</v>
+      </c>
+      <c r="T239">
+        <v>14</v>
+      </c>
+      <c r="V239" t="str">
+        <v>EFECTIVO</v>
+      </c>
+      <c r="W239" t="str">
+        <v>UF</v>
+      </c>
+      <c r="X239" t="str">
+        <v>ACARTERA1</v>
+      </c>
+      <c r="Y239" t="str">
+        <v>ACARTERA1</v>
+      </c>
+      <c r="Z239" t="str">
+        <v>SIN DATOS</v>
+      </c>
+      <c r="AB239" t="str">
+        <v>CajaLider</v>
+      </c>
+      <c r="AC239" t="str">
+        <v>SIN DATOS</v>
+      </c>
+      <c r="AD239" t="str">
+        <v>HASTA 30 D</v>
+      </c>
+      <c r="AE239">
+        <v>-298</v>
+      </c>
+      <c r="AF239">
+        <v>1</v>
+      </c>
+      <c r="AG239">
+        <v>0</v>
+      </c>
+      <c r="AH239" t="str">
+        <v>Cuota periódica</v>
+      </c>
+      <c r="AI239" t="str">
+        <v>C.I.</v>
+      </c>
+      <c r="AJ239" t="str">
+        <v>Cobro</v>
+      </c>
+      <c r="AK239">
+        <v>221086</v>
+      </c>
+      <c r="AM239">
+        <v>80</v>
+      </c>
+      <c r="AQ239" t="str">
+        <v>CATEGORIA 2 UF - PROP: 313 - 3910.000000000000</v>
+      </c>
+      <c r="AR239" t="str">
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
+      </c>
+      <c r="AT239" t="str">
+        <v>56999664236</v>
+      </c>
+      <c r="AU239" t="str">
+        <v>SEPULTURA</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>VALLES UNIDOS S.A.</v>
+      </c>
+      <c r="B240" t="str">
+        <v>210394818</v>
+      </c>
+      <c r="C240" t="str">
+        <v>BRICEÑO VENEGAS BASTIAN FELIPE</v>
+      </c>
+      <c r="D240" t="str">
+        <v>Metropolitana</v>
+      </c>
+      <c r="E240" t="str">
+        <v>Quilicura</v>
+      </c>
+      <c r="F240" t="str">
+        <v>VALLES UNIDOS CENTRO</v>
+      </c>
+      <c r="G240">
+        <v>1014772</v>
+      </c>
+      <c r="H240" t="str">
+        <v>ACTIVO VALIDADO</v>
+      </c>
+      <c r="I240">
+        <v>97814</v>
+      </c>
+      <c r="J240">
+        <v>2.38</v>
+      </c>
+      <c r="K240">
+        <v>5</v>
+      </c>
+      <c r="L240">
+        <v>31</v>
+      </c>
+      <c r="M240" t="str">
+        <v>05/10/2026</v>
+      </c>
+      <c r="N240">
+        <v>2.38</v>
+      </c>
+      <c r="O240">
+        <v>97814</v>
+      </c>
+      <c r="P240" t="str">
+        <v>SIN DATOS</v>
+      </c>
+      <c r="Q240">
+        <v>4</v>
+      </c>
+      <c r="R240">
+        <v>1</v>
+      </c>
+      <c r="S240">
+        <v>41098.15</v>
+      </c>
+      <c r="T240">
+        <v>1</v>
+      </c>
+      <c r="U240" t="str">
+        <v>OFICINA</v>
+      </c>
+      <c r="V240" t="str">
+        <v>BANCO ESTADO</v>
+      </c>
+      <c r="W240" t="str">
+        <v>UF</v>
+      </c>
+      <c r="X240" t="str">
+        <v>ACARTERA1</v>
+      </c>
+      <c r="Y240" t="str">
+        <v>ACARTERA1</v>
+      </c>
+      <c r="Z240" t="str">
+        <v>SIN DATOS</v>
+      </c>
+      <c r="AB240" t="str">
+        <v>CajaLider</v>
+      </c>
+      <c r="AC240" t="str">
+        <v>SIN DATOS</v>
+      </c>
+      <c r="AD240" t="str">
+        <v>AL DIA</v>
+      </c>
+      <c r="AE240">
+        <v>-390</v>
+      </c>
+      <c r="AF240">
+        <v>1</v>
+      </c>
+      <c r="AG240">
+        <v>0</v>
+      </c>
+      <c r="AH240" t="str">
+        <v>Cuota periódica</v>
+      </c>
+      <c r="AI240" t="str">
+        <v>C.I.</v>
+      </c>
+      <c r="AJ240" t="str">
+        <v>Cobro</v>
+      </c>
+      <c r="AK240">
         <v>221093</v>
       </c>
-      <c r="AM238">
+      <c r="AM240">
         <v>16463</v>
       </c>
-      <c r="AQ238" t="str">
+      <c r="AQ240" t="str">
         <v>MANT 2 UF NF</v>
       </c>
-      <c r="AR238" t="str">
-        <v>ts.mariasilvalopez@gmail.com</v>
-      </c>
-      <c r="AS238" t="str">
-        <v/>
-      </c>
-      <c r="AT238" t="str">
-        <v>945718455</v>
-      </c>
-      <c r="AU238" t="str">
+      <c r="AR240" t="str">
+        <v>CARRASCOSANTIAGO05@GMAIL.COM</v>
+      </c>
+      <c r="AT240" t="str">
+        <v>56999664236</v>
+      </c>
+      <c r="AU240" t="str">
         <v>SEPULTURA</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AU238"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AU240"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -30532,13 +30677,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53631902-2543-4C3D-A4C4-0936E81A131D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E10343C8-912E-4494-A7B1-4EDEEADBA79F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EC133BE-898D-4321-925A-4A93D990E1AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5E399B3-7BF9-46F8-94E5-C3CC5C63E70C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4077D991-600D-43F1-9EBB-43FB1EDBC28D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10FADE58-FCE5-45DE-988F-05FC3509EBD0}"/>
 </file>